--- a/regularisation_ORMES_A_2025.xlsx
+++ b/regularisation_ORMES_A_2025.xlsx
@@ -7,9 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Paramètres" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Récapitulatif 2025" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Récapitulatif 2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Paramètres" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="C1 C2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="C3 C4 C5" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Vacance Locative" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,14 +21,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;(#,##0.00)"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="168" formatCode="0.00000"/>
-    <numFmt numFmtId="169" formatCode="0.00000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00&quot; €&quot;"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,14 +44,7 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="001B3A6B"/>
       <sz val="9"/>
     </font>
     <font>
@@ -60,19 +55,14 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00000000"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="001B3A6B"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -83,6 +73,12 @@
     <font>
       <name val="Calibri"/>
       <color rgb="00AAAAAA"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
@@ -102,8 +98,19 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00666666"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -117,7 +124,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D0DDEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="002E5FA3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F4F8"/>
       </patternFill>
     </fill>
     <fill>
@@ -132,12 +149,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0DDEF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F4F8"/>
+        <fgColor rgb="00E64A19"/>
       </patternFill>
     </fill>
   </fills>
@@ -153,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -161,16 +173,41 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -182,66 +219,79 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -609,175 +659,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="27.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ORMES A — PARAMÈTRES SITE 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15.8" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Site</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>ORMES A</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15.8" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Surface totale site (m²)</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>29565.91</v>
-      </c>
-    </row>
-    <row r="4" ht="15.8" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Année</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="5" ht="7.55" customHeight="1"/>
-    <row r="6" ht="19.55" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Lot</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Statut</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Surface (m²)</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Bâtiment</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Locataire</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Début de bail</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Fin de bail</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>Début effectif (MAD/bail)</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>Fin effective</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15.05" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>C1 C2</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Occupé</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>9623</v>
-      </c>
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>ID LOGISTICS</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>45737</v>
-      </c>
-      <c r="G7" s="10" t="n">
-        <v>50119</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>45737</v>
-      </c>
-      <c r="I7" s="10" t="n">
-        <v>50119</v>
-      </c>
-    </row>
-    <row r="8" ht="15.05" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>C3 C4 C5</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>Vacant</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>19942.91</v>
-      </c>
-      <c r="D8" s="8" t="inlineStr"/>
-      <c r="E8" s="9" t="inlineStr"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -798,2571 +679,2571 @@
       </c>
     </row>
     <row r="2" ht="15.8" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Site : ORMES A  |  Période : 01/01/2025 – 31/12/2025</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19.55" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Fournisseur</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Date facture</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>N° facture</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Montant HT (€)</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>TVA (€)</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Montant TTC (€)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="21.75" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>── FLUIDES ──</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Eau</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15.05" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>AQUALIGE</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n"/>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>1096904376-1</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Mise en service</t>
         </is>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="8" t="n">
         <v>49.82</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="8" t="n">
         <v>4.98</v>
       </c>
-      <c r="G6" s="16" t="n">
+      <c r="G6" s="8" t="n">
         <v>54.8</v>
       </c>
     </row>
     <row r="7" ht="15.05" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>AQUALIGE</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n"/>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>1096892743-1</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Mise en service</t>
         </is>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="8" t="n">
         <v>49.82</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="8" t="n">
         <v>4.98</v>
       </c>
-      <c r="G7" s="16" t="n">
+      <c r="G7" s="8" t="n">
         <v>54.8</v>
       </c>
     </row>
     <row r="8" ht="15.05" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>AQUALIGE</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="9" t="n">
         <v>45854</v>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>1099190061</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>EAU ET ASSAINISSEMENT COMPTEUR 124MK046246</t>
         </is>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="8" t="n">
         <v>645.02</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="8" t="n">
         <v>46.22</v>
       </c>
-      <c r="G8" s="16" t="n">
+      <c r="G8" s="8" t="n">
         <v>691.24</v>
       </c>
     </row>
     <row r="9" ht="15.05" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>AQUALIGE</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="9" t="n">
         <v>45854</v>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>1099203459</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">EAU ET ASSAINISSEMENT COMPTEUR C24FE015783 </t>
         </is>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="8" t="n">
         <v>292.74</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="8" t="n">
         <v>21.75</v>
       </c>
-      <c r="G9" s="16" t="n">
+      <c r="G9" s="8" t="n">
         <v>314.49</v>
       </c>
     </row>
     <row r="10" ht="15.8" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    Sous-total — Eau</t>
         </is>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="11">
         <f>SUM(E6:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="11">
         <f>SUM(F6:F9)</f>
         <v/>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="11">
         <f>SUM(G6:G9)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Electricité</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15.05" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>ENGIE</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
+      <c r="B12" s="9" t="n">
         <v>45780</v>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>1200009625875</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>CONSOMMATIONS ELECTRICITE 01/04/2025 au 30/04/2025</t>
         </is>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="8" t="n">
         <v>4337.28</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="8" t="n">
         <v>867.46</v>
       </c>
-      <c r="G12" s="16" t="n">
+      <c r="G12" s="8" t="n">
         <v>5204.74</v>
       </c>
     </row>
     <row r="13" ht="15.05" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>ENGIE</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n">
+      <c r="B13" s="9" t="n">
         <v>45813</v>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>40017044367</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">CONSOMMATIONS ELECTRICTITE </t>
         </is>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="8" t="n">
         <v>3646.51</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="8" t="n">
         <v>729.3</v>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="8" t="n">
         <v>4375.81</v>
       </c>
     </row>
     <row r="14" ht="15.05" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>ENGIE</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="9" t="n">
         <v>45843</v>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>520002087186</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">CONSOMMATIONS ELECTRICTITE </t>
         </is>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="8" t="n">
         <v>3379.85</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="8" t="n">
         <v>675.97</v>
       </c>
-      <c r="G14" s="16" t="n">
+      <c r="G14" s="8" t="n">
         <v>4055.82</v>
       </c>
     </row>
     <row r="15" ht="15.05" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>ENGIE</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
+      <c r="B15" s="9" t="n">
         <v>45876</v>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>320007792334</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">CONSOMMATIONS ELECTRICTITE </t>
         </is>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="8" t="n">
         <v>3600.2</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="8" t="n">
         <v>720.04</v>
       </c>
-      <c r="G15" s="16" t="n">
+      <c r="G15" s="8" t="n">
         <v>4320.24</v>
       </c>
     </row>
     <row r="16" ht="15.05" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>ENGIE</t>
         </is>
       </c>
-      <c r="B16" s="17" t="n">
+      <c r="B16" s="9" t="n">
         <v>45904</v>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>760000335269</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">CONSOMMATIONS ELECTRICTITE </t>
         </is>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="8" t="n">
         <v>3715.72</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="8" t="n">
         <v>743.14</v>
       </c>
-      <c r="G16" s="16" t="n">
+      <c r="G16" s="8" t="n">
         <v>4458.86</v>
       </c>
     </row>
     <row r="17" ht="15.05" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>ENGIE</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n">
+      <c r="B17" s="9" t="n">
         <v>45934</v>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>630000369535</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">CONSOMMATIONS ELECTRICTITE </t>
         </is>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="8" t="n">
         <v>3737.12</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="8" t="n">
         <v>747.42</v>
       </c>
-      <c r="G17" s="16" t="n">
+      <c r="G17" s="8" t="n">
         <v>4484.54</v>
       </c>
     </row>
     <row r="18" ht="15.05" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>ENGIE</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n">
+      <c r="B18" s="9" t="n">
         <v>45965</v>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>690000378639</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">CONSOMMATIONS ELECTRICTITE </t>
         </is>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="8" t="n">
         <v>4184.89</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="8" t="n">
         <v>836.98</v>
       </c>
-      <c r="G18" s="16" t="n">
+      <c r="G18" s="8" t="n">
         <v>5021.870000000001</v>
       </c>
     </row>
     <row r="19" ht="15.05" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>ENGIE</t>
         </is>
       </c>
-      <c r="B19" s="17" t="n">
+      <c r="B19" s="9" t="n">
         <v>45995</v>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>670000394240</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">CONSOMMATIONS ELECTRICTITE </t>
         </is>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="8" t="n">
         <v>6650.18</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="8" t="n">
         <v>1330.04</v>
       </c>
-      <c r="G19" s="16" t="n">
+      <c r="G19" s="8" t="n">
         <v>7980.22</v>
       </c>
     </row>
     <row r="20" ht="15.05" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>ENGIE</t>
         </is>
       </c>
-      <c r="B20" s="17" t="n">
+      <c r="B20" s="9" t="n">
         <v>46025</v>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>980006173374</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">CONSOMMATIONS ELECTRICTITE </t>
         </is>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="8" t="n">
         <v>7445.64</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="8" t="n">
         <v>1489.13</v>
       </c>
-      <c r="G20" s="16" t="n">
+      <c r="G20" s="8" t="n">
         <v>8934.77</v>
       </c>
     </row>
     <row r="21" ht="15.8" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    Sous-total — Electricité</t>
         </is>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="11">
         <f>SUM(E12:E20)</f>
         <v/>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="11">
         <f>SUM(F12:F20)</f>
         <v/>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="11">
         <f>SUM(G12:G20)</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Gaz</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.05" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>ENGIE</t>
         </is>
       </c>
-      <c r="B23" s="17" t="n">
+      <c r="B23" s="9" t="n">
         <v>45782</v>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>680000258800</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>CONSOMMATIONS GAZ 02/04/2025 au 01/05/2025</t>
         </is>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="8" t="n">
         <v>2147.53</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="F23" s="8" t="n">
         <v>160.14</v>
       </c>
-      <c r="G23" s="16" t="n">
+      <c r="G23" s="8" t="n">
         <v>2307.67</v>
       </c>
     </row>
     <row r="24" ht="15.05" customHeight="1">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>ENGIE</t>
         </is>
       </c>
-      <c r="B24" s="17" t="n">
+      <c r="B24" s="9" t="n">
         <v>45813</v>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>780000262507</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>CONSOMMATIONS GAZ</t>
         </is>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="E24" s="8" t="n">
         <v>2039.74</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="F24" s="8" t="n">
         <v>125.43</v>
       </c>
-      <c r="G24" s="16" t="n">
+      <c r="G24" s="8" t="n">
         <v>2165.17</v>
       </c>
     </row>
     <row r="25" ht="15.05" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>ENGIE</t>
         </is>
       </c>
-      <c r="B25" s="17" t="n">
+      <c r="B25" s="9" t="n">
         <v>45842</v>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>820001240297</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>CONSOMMATIONS GAZ</t>
         </is>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="E25" s="8" t="n">
         <v>2039.74</v>
       </c>
-      <c r="F25" s="16" t="n">
+      <c r="F25" s="8" t="n">
         <v>125.43</v>
       </c>
-      <c r="G25" s="16" t="n">
+      <c r="G25" s="8" t="n">
         <v>2165.17</v>
       </c>
     </row>
     <row r="26" ht="15.05" customHeight="1">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>ENGIE</t>
         </is>
       </c>
-      <c r="B26" s="17" t="n">
+      <c r="B26" s="9" t="n">
         <v>45873</v>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>40017074775</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>CONSOMMATIONS GAZ</t>
         </is>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="E26" s="8" t="n">
         <v>2048.67</v>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="F26" s="8" t="n">
         <v>126.15</v>
       </c>
-      <c r="G26" s="16" t="n">
+      <c r="G26" s="8" t="n">
         <v>2174.82</v>
       </c>
     </row>
     <row r="27" ht="15.05" customHeight="1">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>ENGIE</t>
         </is>
       </c>
-      <c r="B27" s="17" t="n">
+      <c r="B27" s="9" t="n">
         <v>45904</v>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>65000032141</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>CONSOMMATIONS GAZ</t>
         </is>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="E27" s="8" t="n">
         <v>2048.67</v>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="F27" s="8" t="n">
         <v>409.73</v>
       </c>
-      <c r="G27" s="16" t="n">
+      <c r="G27" s="8" t="n">
         <v>2458.4</v>
       </c>
     </row>
     <row r="28" ht="15.05" customHeight="1">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>ENGIE</t>
         </is>
       </c>
-      <c r="B28" s="17" t="n">
+      <c r="B28" s="9" t="n">
         <v>45934</v>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>420006908243</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>CONSOMMATIONS GAZ</t>
         </is>
       </c>
-      <c r="E28" s="16" t="n">
+      <c r="E28" s="8" t="n">
         <v>2048.67</v>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="F28" s="8" t="n">
         <v>409.73</v>
       </c>
-      <c r="G28" s="16" t="n">
+      <c r="G28" s="8" t="n">
         <v>2458.4</v>
       </c>
     </row>
     <row r="29" ht="15.05" customHeight="1">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>ENGIE</t>
         </is>
       </c>
-      <c r="B29" s="17" t="n">
+      <c r="B29" s="9" t="n">
         <v>45966</v>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>690000380305</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>CONSOMMATIONS GAZ</t>
         </is>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="8" t="n">
         <v>2049.48</v>
       </c>
-      <c r="F29" s="16" t="n">
+      <c r="F29" s="8" t="n">
         <v>409.9</v>
       </c>
-      <c r="G29" s="16" t="n">
+      <c r="G29" s="8" t="n">
         <v>2459.38</v>
       </c>
     </row>
     <row r="30" ht="15.05" customHeight="1">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>ENGIE</t>
         </is>
       </c>
-      <c r="B30" s="17" t="n">
+      <c r="B30" s="9" t="n">
         <v>45995</v>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>820006290113</t>
         </is>
       </c>
-      <c r="D30" s="14" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>CONSOMMATIONS GAZ</t>
         </is>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="E30" s="8" t="n">
         <v>2055.74</v>
       </c>
-      <c r="F30" s="16" t="n">
+      <c r="F30" s="8" t="n">
         <v>411.15</v>
       </c>
-      <c r="G30" s="16" t="n">
+      <c r="G30" s="8" t="n">
         <v>2466.89</v>
       </c>
     </row>
     <row r="31" ht="15.05" customHeight="1">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>ENGIE</t>
         </is>
       </c>
-      <c r="B31" s="17" t="n">
+      <c r="B31" s="9" t="n">
         <v>46026</v>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>20040377238</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>CONSOMMATIONS GAZ</t>
         </is>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="E31" s="8" t="n">
         <v>2063.48</v>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="F31" s="8" t="n">
         <v>412.7</v>
       </c>
-      <c r="G31" s="16" t="n">
+      <c r="G31" s="8" t="n">
         <v>2476.18</v>
       </c>
     </row>
     <row r="32" ht="15.8" customHeight="1">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    Sous-total — Gaz</t>
         </is>
       </c>
-      <c r="E32" s="19">
+      <c r="E32" s="11">
         <f>SUM(E23:E31)</f>
         <v/>
       </c>
-      <c r="F32" s="19">
+      <c r="F32" s="11">
         <f>SUM(F23:F31)</f>
         <v/>
       </c>
-      <c r="G32" s="19">
+      <c r="G32" s="11">
         <f>SUM(G23:G31)</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="21.75" customHeight="1">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>── TRAVAUX ──</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Entretien Courant</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.05" customHeight="1">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>ESPACE CLOTURE CENTRE</t>
         </is>
       </c>
-      <c r="B35" s="17" t="n">
+      <c r="B35" s="9" t="n">
         <v>45803</v>
       </c>
-      <c r="C35" s="14" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>18011749</t>
         </is>
       </c>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>INSTALLATION BOUCLE SORTIE SUR PORTAIL VL</t>
         </is>
       </c>
-      <c r="E35" s="16" t="n">
+      <c r="E35" s="8" t="n">
         <v>610</v>
       </c>
-      <c r="F35" s="16" t="n">
+      <c r="F35" s="8" t="n">
         <v>122</v>
       </c>
-      <c r="G35" s="16" t="n">
+      <c r="G35" s="8" t="n">
         <v>732</v>
       </c>
     </row>
     <row r="36" ht="15.05" customHeight="1">
-      <c r="A36" s="14" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>ESPACE CLOTURE CENTRE</t>
         </is>
       </c>
-      <c r="B36" s="17" t="n">
+      <c r="B36" s="9" t="n">
         <v>45832</v>
       </c>
-      <c r="C36" s="14" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>18011816</t>
         </is>
       </c>
-      <c r="D36" s="14" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>POSE DIGICODE</t>
         </is>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="E36" s="8" t="n">
         <v>734.4</v>
       </c>
-      <c r="F36" s="16" t="n">
+      <c r="F36" s="8" t="n">
         <v>146.88</v>
       </c>
-      <c r="G36" s="16" t="n">
+      <c r="G36" s="8" t="n">
         <v>881.28</v>
       </c>
     </row>
     <row r="37" ht="15.8" customHeight="1">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    Sous-total — Entretien Courant</t>
         </is>
       </c>
-      <c r="E37" s="19">
+      <c r="E37" s="11">
         <f>SUM(E35:E36)</f>
         <v/>
       </c>
-      <c r="F37" s="19">
+      <c r="F37" s="11">
         <f>SUM(F35:F36)</f>
         <v/>
       </c>
-      <c r="G37" s="19">
+      <c r="G37" s="11">
         <f>SUM(G35:G36)</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="21.75" customHeight="1">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>── CONTRAT MAINTENANCE ──</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Espaces Verts</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.05" customHeight="1">
-      <c r="A40" s="14" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>ARP ASTRANCE</t>
         </is>
       </c>
-      <c r="B40" s="17" t="n">
+      <c r="B40" s="9" t="n">
         <v>45838</v>
       </c>
-      <c r="C40" s="14" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>FC-ARP-25-06-0141</t>
         </is>
       </c>
-      <c r="D40" s="14" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>Suivis écologiques</t>
         </is>
       </c>
-      <c r="E40" s="16" t="n">
+      <c r="E40" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="F40" s="16" t="n">
+      <c r="F40" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="G40" s="16" t="n">
+      <c r="G40" s="8" t="n">
         <v>1800</v>
       </c>
     </row>
     <row r="41" ht="15.05" customHeight="1">
-      <c r="A41" s="14" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>ARP ASTRANCE</t>
         </is>
       </c>
-      <c r="B41" s="17" t="n">
+      <c r="B41" s="9" t="n">
         <v>45869</v>
       </c>
-      <c r="C41" s="14" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>FC-ARP-25-07-0086</t>
         </is>
       </c>
-      <c r="D41" s="14" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>Suivis écologiques</t>
         </is>
       </c>
-      <c r="E41" s="16" t="n">
+      <c r="E41" s="8" t="n">
         <v>2250</v>
       </c>
-      <c r="F41" s="16" t="n">
+      <c r="F41" s="8" t="n">
         <v>450</v>
       </c>
-      <c r="G41" s="16" t="n">
+      <c r="G41" s="8" t="n">
         <v>2700</v>
       </c>
     </row>
     <row r="42" ht="15.05" customHeight="1">
-      <c r="A42" s="14" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>BOURDIN</t>
         </is>
       </c>
-      <c r="B42" s="17" t="n">
+      <c r="B42" s="9" t="n">
         <v>45894</v>
       </c>
-      <c r="C42" s="14" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>BP25080709</t>
         </is>
       </c>
-      <c r="D42" s="14" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>Entretien espaces verts</t>
         </is>
       </c>
-      <c r="E42" s="16" t="n">
+      <c r="E42" s="8" t="n">
         <v>1777.5</v>
       </c>
-      <c r="F42" s="16" t="n">
+      <c r="F42" s="8" t="n">
         <v>355.5</v>
       </c>
-      <c r="G42" s="16" t="n">
+      <c r="G42" s="8" t="n">
         <v>2133</v>
       </c>
     </row>
     <row r="43" ht="15.05" customHeight="1">
-      <c r="A43" s="14" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>ARP ASTRANCE</t>
         </is>
       </c>
-      <c r="B43" s="17" t="n">
+      <c r="B43" s="9" t="n">
         <v>45991</v>
       </c>
-      <c r="C43" s="14" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>FC-ARP-25-11-0060</t>
         </is>
       </c>
-      <c r="D43" s="14" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>Suivis écologiques</t>
         </is>
       </c>
-      <c r="E43" s="16" t="n">
+      <c r="E43" s="8" t="n">
         <v>2450</v>
       </c>
-      <c r="F43" s="16" t="n">
+      <c r="F43" s="8" t="n">
         <v>490</v>
       </c>
-      <c r="G43" s="16" t="n">
+      <c r="G43" s="8" t="n">
         <v>2940</v>
       </c>
     </row>
     <row r="44" ht="15.05" customHeight="1">
-      <c r="A44" s="14" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>BOURDIN</t>
         </is>
       </c>
-      <c r="B44" s="17" t="n">
+      <c r="B44" s="9" t="n">
         <v>45986</v>
       </c>
-      <c r="C44" s="14" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>BP 9000870</t>
         </is>
       </c>
-      <c r="D44" s="14" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>Entretien espaces verts</t>
         </is>
       </c>
-      <c r="E44" s="16" t="n">
+      <c r="E44" s="8" t="n">
         <v>1777.5</v>
       </c>
-      <c r="F44" s="16" t="n">
+      <c r="F44" s="8" t="n">
         <v>355.5</v>
       </c>
-      <c r="G44" s="16" t="n">
+      <c r="G44" s="8" t="n">
         <v>2133</v>
       </c>
     </row>
     <row r="45" ht="15.05" customHeight="1">
-      <c r="A45" s="14" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>ARP.Astrance</t>
         </is>
       </c>
-      <c r="B45" s="17" t="n">
+      <c r="B45" s="9" t="n">
         <v>45961</v>
       </c>
-      <c r="C45" s="14" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>FC-ARP-25-10-0205</t>
         </is>
       </c>
-      <c r="D45" s="14" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>Mission d'assistance à maîtrise d'ouvrage pour la réalisation de suivi écologiques</t>
         </is>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="E45" s="8" t="n">
         <v>562.5</v>
       </c>
-      <c r="F45" s="16" t="n">
+      <c r="F45" s="8" t="n">
         <v>112.5</v>
       </c>
-      <c r="G45" s="16" t="n">
+      <c r="G45" s="8" t="n">
         <v>675</v>
       </c>
     </row>
     <row r="46" ht="15.8" customHeight="1">
-      <c r="A46" s="18" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    Sous-total — Espaces Verts</t>
         </is>
       </c>
-      <c r="E46" s="19">
+      <c r="E46" s="11">
         <f>SUM(E40:E45)</f>
         <v/>
       </c>
-      <c r="F46" s="19">
+      <c r="F46" s="11">
         <f>SUM(F40:F45)</f>
         <v/>
       </c>
-      <c r="G46" s="19">
+      <c r="G46" s="11">
         <f>SUM(G40:G45)</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  CVC</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.05" customHeight="1">
-      <c r="A48" s="14" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>EIFFAGE</t>
         </is>
       </c>
-      <c r="B48" s="17" t="n">
+      <c r="B48" s="9" t="n">
         <v>45841</v>
       </c>
-      <c r="C48" s="14" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>F00190250700001</t>
         </is>
       </c>
-      <c r="D48" s="14" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>MAINTENANCE CVC CHAUFFERIE CLIMATISATION VRD PLOMBERIE</t>
         </is>
       </c>
-      <c r="E48" s="16" t="n">
+      <c r="E48" s="8" t="n">
         <v>3430</v>
       </c>
-      <c r="F48" s="16" t="n">
+      <c r="F48" s="8" t="n">
         <v>686</v>
       </c>
-      <c r="G48" s="16" t="n">
+      <c r="G48" s="8" t="n">
         <v>4116</v>
       </c>
     </row>
     <row r="49" ht="15.05" customHeight="1">
-      <c r="A49" s="14" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>EIFFAGE</t>
         </is>
       </c>
-      <c r="B49" s="17" t="n">
+      <c r="B49" s="9" t="n">
         <v>45988</v>
       </c>
-      <c r="C49" s="14" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>F00190251100472</t>
         </is>
       </c>
-      <c r="D49" s="14" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>REGULARISATION DEFAUT POMPE DE RELEVAGE</t>
         </is>
       </c>
-      <c r="E49" s="16" t="n">
+      <c r="E49" s="8" t="n">
         <v>250</v>
       </c>
-      <c r="F49" s="16" t="n">
+      <c r="F49" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="G49" s="16" t="n">
+      <c r="G49" s="8" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="50" ht="15.8" customHeight="1">
-      <c r="A50" s="18" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    Sous-total — CVC</t>
         </is>
       </c>
-      <c r="E50" s="19">
+      <c r="E50" s="11">
         <f>SUM(E48:E49)</f>
         <v/>
       </c>
-      <c r="F50" s="19">
+      <c r="F50" s="11">
         <f>SUM(F48:F49)</f>
         <v/>
       </c>
-      <c r="G50" s="19">
+      <c r="G50" s="11">
         <f>SUM(G48:G49)</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Sécurité</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15.05" customHeight="1">
-      <c r="A52" s="14" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>AVC Sécurité</t>
         </is>
       </c>
-      <c r="B52" s="17" t="n">
+      <c r="B52" s="9" t="n">
         <v>45776</v>
       </c>
-      <c r="C52" s="14" t="inlineStr"/>
-      <c r="D52" s="14" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr"/>
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>CONTRAT DE TELESURVEILLANCE + GSM</t>
         </is>
       </c>
-      <c r="E52" s="16" t="n">
+      <c r="E52" s="8" t="n">
         <v>840</v>
       </c>
-      <c r="F52" s="16" t="n">
+      <c r="F52" s="8" t="n">
         <v>168</v>
       </c>
-      <c r="G52" s="16" t="n">
+      <c r="G52" s="8" t="n">
         <v>1008</v>
       </c>
     </row>
     <row r="53" ht="15.05" customHeight="1">
-      <c r="A53" s="14" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>AVC Sécurité</t>
         </is>
       </c>
-      <c r="B53" s="17" t="n">
+      <c r="B53" s="9" t="n">
         <v>45747</v>
       </c>
-      <c r="C53" s="14" t="inlineStr"/>
-      <c r="D53" s="14" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr"/>
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>CONTRAT DE TELESURVEILLANCE + GSM</t>
         </is>
       </c>
-      <c r="E53" s="16" t="n">
+      <c r="E53" s="8" t="n">
         <v>840</v>
       </c>
-      <c r="F53" s="16" t="n">
+      <c r="F53" s="8" t="n">
         <v>168</v>
       </c>
-      <c r="G53" s="16" t="n">
+      <c r="G53" s="8" t="n">
         <v>1008</v>
       </c>
     </row>
     <row r="54" ht="15.8" customHeight="1">
-      <c r="A54" s="18" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    Sous-total — Sécurité</t>
         </is>
       </c>
-      <c r="E54" s="19">
+      <c r="E54" s="11">
         <f>SUM(E52:E53)</f>
         <v/>
       </c>
-      <c r="F54" s="19">
+      <c r="F54" s="11">
         <f>SUM(F52:F53)</f>
         <v/>
       </c>
-      <c r="G54" s="19">
+      <c r="G54" s="11">
         <f>SUM(G52:G53)</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  SSI</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15.05" customHeight="1">
-      <c r="A56" s="14" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>CONCEPT SECURITE</t>
         </is>
       </c>
-      <c r="B56" s="17" t="n">
+      <c r="B56" s="9" t="n">
         <v>45832</v>
       </c>
-      <c r="C56" s="14" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>FA022398</t>
         </is>
       </c>
-      <c r="D56" s="14" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t>DEPANNAGE SSI - EXERCICE ID LOGISTICS</t>
         </is>
       </c>
-      <c r="E56" s="16" t="n">
+      <c r="E56" s="8" t="n">
         <v>304</v>
       </c>
-      <c r="F56" s="16" t="n">
+      <c r="F56" s="8" t="n">
         <v>60.8</v>
       </c>
-      <c r="G56" s="16" t="n">
+      <c r="G56" s="8" t="n">
         <v>364.8</v>
       </c>
     </row>
     <row r="57" ht="15.05" customHeight="1">
-      <c r="A57" s="14" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>CONCEPT SECURITE</t>
         </is>
       </c>
-      <c r="B57" s="17" t="n">
+      <c r="B57" s="9" t="n">
         <v>45929</v>
       </c>
-      <c r="C57" s="14" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>FA022971</t>
         </is>
       </c>
-      <c r="D57" s="14" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>Fourniture des pose des extincteurs parties communes</t>
         </is>
       </c>
-      <c r="E57" s="16" t="n">
+      <c r="E57" s="8" t="n">
         <v>922.0700000000001</v>
       </c>
-      <c r="F57" s="16" t="n">
+      <c r="F57" s="8" t="n">
         <v>184.41</v>
       </c>
-      <c r="G57" s="16" t="n">
+      <c r="G57" s="8" t="n">
         <v>1106.48</v>
       </c>
     </row>
     <row r="58" ht="15.05" customHeight="1">
-      <c r="A58" s="14" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>CONCEPT SECURITE</t>
         </is>
       </c>
-      <c r="B58" s="17" t="n">
+      <c r="B58" s="9" t="n">
         <v>45936</v>
       </c>
-      <c r="C58" s="14" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>FA023051</t>
         </is>
       </c>
-      <c r="D58" s="14" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t>Dépannage porte coupe-feu et porte piétonne</t>
         </is>
       </c>
-      <c r="E58" s="16" t="n">
+      <c r="E58" s="8" t="n">
         <v>194</v>
       </c>
-      <c r="F58" s="16" t="n">
+      <c r="F58" s="8" t="n">
         <v>38.8</v>
       </c>
-      <c r="G58" s="16" t="n">
+      <c r="G58" s="8" t="n">
         <v>232.8</v>
       </c>
     </row>
     <row r="59" ht="15.8" customHeight="1">
-      <c r="A59" s="18" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    Sous-total — SSI</t>
         </is>
       </c>
-      <c r="E59" s="19">
+      <c r="E59" s="11">
         <f>SUM(E56:E58)</f>
         <v/>
       </c>
-      <c r="F59" s="19">
+      <c r="F59" s="11">
         <f>SUM(F56:F58)</f>
         <v/>
       </c>
-      <c r="G59" s="19">
+      <c r="G59" s="11">
         <f>SUM(G56:G58)</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Toitures</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15.05" customHeight="1">
-      <c r="A61" s="14" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>SIPHOTEC</t>
         </is>
       </c>
-      <c r="B61" s="17" t="n">
+      <c r="B61" s="9" t="n">
         <v>45838</v>
       </c>
-      <c r="C61" s="14" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>FE2506737</t>
         </is>
       </c>
-      <c r="D61" s="14" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t>ENTRETIEN SIPHOÏDES</t>
         </is>
       </c>
-      <c r="E61" s="16" t="n">
+      <c r="E61" s="8" t="n">
         <v>2600</v>
       </c>
-      <c r="F61" s="16" t="n">
+      <c r="F61" s="8" t="n">
         <v>520</v>
       </c>
-      <c r="G61" s="16" t="n">
+      <c r="G61" s="8" t="n">
         <v>3120</v>
       </c>
     </row>
     <row r="62" ht="15.05" customHeight="1">
-      <c r="A62" s="14" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>SIPHOTEC</t>
         </is>
       </c>
-      <c r="B62" s="17" t="n">
+      <c r="B62" s="9" t="n">
         <v>45961</v>
       </c>
-      <c r="C62" s="14" t="inlineStr">
+      <c r="C62" s="6" t="inlineStr">
         <is>
           <t>FE2510768</t>
         </is>
       </c>
-      <c r="D62" s="14" t="inlineStr">
+      <c r="D62" s="6" t="inlineStr">
         <is>
           <t>ENTRETIEN DU SYSTÈME SIPHOIDE</t>
         </is>
       </c>
-      <c r="E62" s="16" t="n">
+      <c r="E62" s="8" t="n">
         <v>2600</v>
       </c>
-      <c r="F62" s="16" t="n">
+      <c r="F62" s="8" t="n">
         <v>520</v>
       </c>
-      <c r="G62" s="16" t="n">
+      <c r="G62" s="8" t="n">
         <v>3120</v>
       </c>
     </row>
     <row r="63" ht="15.05" customHeight="1">
-      <c r="A63" s="14" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>PROTECTA</t>
         </is>
       </c>
-      <c r="B63" s="17" t="n">
+      <c r="B63" s="9" t="n">
         <v>46014</v>
       </c>
-      <c r="C63" s="14" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>FA-45-2025-0564</t>
         </is>
       </c>
-      <c r="D63" s="14" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>VISITE TOITURE / RAPPORT PHOTO</t>
         </is>
       </c>
-      <c r="E63" s="16" t="n">
+      <c r="E63" s="8" t="n">
         <v>1125.66</v>
       </c>
-      <c r="F63" s="16" t="n">
+      <c r="F63" s="8" t="n">
         <v>225.13</v>
       </c>
-      <c r="G63" s="16" t="n">
+      <c r="G63" s="8" t="n">
         <v>1350.79</v>
       </c>
     </row>
     <row r="64" ht="15.8" customHeight="1">
-      <c r="A64" s="18" t="inlineStr">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    Sous-total — Toitures</t>
         </is>
       </c>
-      <c r="E64" s="19">
+      <c r="E64" s="11">
         <f>SUM(E61:E63)</f>
         <v/>
       </c>
-      <c r="F64" s="19">
+      <c r="F64" s="11">
         <f>SUM(F61:F63)</f>
         <v/>
       </c>
-      <c r="G64" s="19">
+      <c r="G64" s="11">
         <f>SUM(G61:G63)</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  SPK / RIA / PI</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15.05" customHeight="1">
-      <c r="A66" s="14" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>AXIMA</t>
         </is>
       </c>
-      <c r="B66" s="17" t="n">
+      <c r="B66" s="9" t="n">
         <v>45750</v>
       </c>
-      <c r="C66" s="14" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>8710250910</t>
         </is>
       </c>
-      <c r="D66" s="14" t="inlineStr">
+      <c r="D66" s="6" t="inlineStr">
         <is>
           <t>CONTRAT D’ENTRETIEN DE PROTECTION INCENDIE du 21/03/25 au 20/04/25</t>
         </is>
       </c>
-      <c r="E66" s="16" t="n">
+      <c r="E66" s="8" t="n">
         <v>2224.33</v>
       </c>
-      <c r="F66" s="16" t="n">
+      <c r="F66" s="8" t="n">
         <v>444.87</v>
       </c>
-      <c r="G66" s="16" t="n">
+      <c r="G66" s="8" t="n">
         <v>2669.2</v>
       </c>
     </row>
     <row r="67" ht="15.05" customHeight="1">
-      <c r="A67" s="14" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>AXIMA</t>
         </is>
       </c>
-      <c r="B67" s="17" t="n">
+      <c r="B67" s="9" t="n">
         <v>45768</v>
       </c>
-      <c r="C67" s="14" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>8710250911</t>
         </is>
       </c>
-      <c r="D67" s="14" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>CONTRAT D’ENTRETIEN DE PROTECTION INCENDIE du 21/04/25 au 20/05/25</t>
         </is>
       </c>
-      <c r="E67" s="16" t="n">
+      <c r="E67" s="8" t="n">
         <v>2224.33</v>
       </c>
-      <c r="F67" s="16" t="n">
+      <c r="F67" s="8" t="n">
         <v>444.87</v>
       </c>
-      <c r="G67" s="16" t="n">
+      <c r="G67" s="8" t="n">
         <v>2669.2</v>
       </c>
     </row>
     <row r="68" ht="15.05" customHeight="1">
-      <c r="A68" s="14" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>AXIMA</t>
         </is>
       </c>
-      <c r="B68" s="17" t="n">
+      <c r="B68" s="9" t="n">
         <v>45798</v>
       </c>
-      <c r="C68" s="14" t="inlineStr">
+      <c r="C68" s="6" t="inlineStr">
         <is>
           <t>8710252246</t>
         </is>
       </c>
-      <c r="D68" s="14" t="inlineStr">
+      <c r="D68" s="6" t="inlineStr">
         <is>
           <t>ENTRETIEN PROTECTION INCENDIE</t>
         </is>
       </c>
-      <c r="E68" s="16" t="n">
+      <c r="E68" s="8" t="n">
         <v>2224.33</v>
       </c>
-      <c r="F68" s="16" t="n">
+      <c r="F68" s="8" t="n">
         <v>444.87</v>
       </c>
-      <c r="G68" s="16" t="n">
+      <c r="G68" s="8" t="n">
         <v>2669.2</v>
       </c>
     </row>
     <row r="69" ht="15.05" customHeight="1">
-      <c r="A69" s="14" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>AXIMA</t>
         </is>
       </c>
-      <c r="B69" s="17" t="n">
+      <c r="B69" s="9" t="n">
         <v>45829</v>
       </c>
-      <c r="C69" s="14" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>8710253747</t>
         </is>
       </c>
-      <c r="D69" s="14" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
         <is>
           <t>ENTRETIEN PROTECTION INCENDIE</t>
         </is>
       </c>
-      <c r="E69" s="16" t="n">
+      <c r="E69" s="8" t="n">
         <v>2224.33</v>
       </c>
-      <c r="F69" s="16" t="n">
+      <c r="F69" s="8" t="n">
         <v>444.87</v>
       </c>
-      <c r="G69" s="16" t="n">
+      <c r="G69" s="8" t="n">
         <v>2669.2</v>
       </c>
     </row>
     <row r="70" ht="15.05" customHeight="1">
-      <c r="A70" s="14" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>AXIMA</t>
         </is>
       </c>
-      <c r="B70" s="17" t="n">
+      <c r="B70" s="9" t="n">
         <v>45864</v>
       </c>
-      <c r="C70" s="14" t="inlineStr">
+      <c r="C70" s="6" t="inlineStr">
         <is>
           <t>8710255568</t>
         </is>
       </c>
-      <c r="D70" s="14" t="inlineStr">
+      <c r="D70" s="6" t="inlineStr">
         <is>
           <t>ENTRETIEN PROTECTION INCENDIE</t>
         </is>
       </c>
-      <c r="E70" s="16" t="n">
+      <c r="E70" s="8" t="n">
         <v>2224.33</v>
       </c>
-      <c r="F70" s="16" t="n">
+      <c r="F70" s="8" t="n">
         <v>444.87</v>
       </c>
-      <c r="G70" s="16" t="n">
+      <c r="G70" s="8" t="n">
         <v>2669.2</v>
       </c>
     </row>
     <row r="71" ht="15.05" customHeight="1">
-      <c r="A71" s="14" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>AXIMA</t>
         </is>
       </c>
-      <c r="B71" s="17" t="n">
+      <c r="B71" s="9" t="n">
         <v>45870</v>
       </c>
-      <c r="C71" s="14" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>8710257942</t>
         </is>
       </c>
-      <c r="D71" s="14" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t>Fourniture de gasoil - protection incendie</t>
         </is>
       </c>
-      <c r="E71" s="16" t="n">
+      <c r="E71" s="8" t="n">
         <v>2656.4</v>
       </c>
-      <c r="F71" s="16" t="n">
+      <c r="F71" s="8" t="n">
         <v>531.28</v>
       </c>
-      <c r="G71" s="16" t="n">
+      <c r="G71" s="8" t="n">
         <v>3187.68</v>
       </c>
     </row>
     <row r="72" ht="15.05" customHeight="1">
-      <c r="A72" s="14" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>AXIMA</t>
         </is>
       </c>
-      <c r="B72" s="17" t="n">
+      <c r="B72" s="9" t="n">
         <v>45890</v>
       </c>
-      <c r="C72" s="14" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t>8710257717</t>
         </is>
       </c>
-      <c r="D72" s="14" t="inlineStr">
+      <c r="D72" s="6" t="inlineStr">
         <is>
           <t>ENTRETIEN PROTECTION INCENDIE</t>
         </is>
       </c>
-      <c r="E72" s="16" t="n">
+      <c r="E72" s="8" t="n">
         <v>2224.33</v>
       </c>
-      <c r="F72" s="16" t="n">
+      <c r="F72" s="8" t="n">
         <v>444.87</v>
       </c>
-      <c r="G72" s="16" t="n">
+      <c r="G72" s="8" t="n">
         <v>2669.2</v>
       </c>
     </row>
     <row r="73" ht="15.05" customHeight="1">
-      <c r="A73" s="14" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>AXIMA</t>
         </is>
       </c>
-      <c r="B73" s="17" t="n">
+      <c r="B73" s="9" t="n">
         <v>45921</v>
       </c>
-      <c r="C73" s="14" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>8710259036</t>
         </is>
       </c>
-      <c r="D73" s="14" t="inlineStr">
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>ENTRETIEN PROTECTION INCENDIE</t>
         </is>
       </c>
-      <c r="E73" s="16" t="n">
+      <c r="E73" s="8" t="n">
         <v>2224.33</v>
       </c>
-      <c r="F73" s="16" t="n">
+      <c r="F73" s="8" t="n">
         <v>444.87</v>
       </c>
-      <c r="G73" s="16" t="n">
+      <c r="G73" s="8" t="n">
         <v>2669.2</v>
       </c>
     </row>
     <row r="74" ht="15.05" customHeight="1">
-      <c r="A74" s="14" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>AXIMA</t>
         </is>
       </c>
-      <c r="B74" s="17" t="n">
+      <c r="B74" s="9" t="n">
         <v>45951</v>
       </c>
-      <c r="C74" s="14" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>8710260974</t>
         </is>
       </c>
-      <c r="D74" s="14" t="inlineStr">
+      <c r="D74" s="6" t="inlineStr">
         <is>
           <t>ENTRETIEN PROTECTION INCENDIE</t>
         </is>
       </c>
-      <c r="E74" s="16" t="n">
+      <c r="E74" s="8" t="n">
         <v>2224.33</v>
       </c>
-      <c r="F74" s="16" t="n">
+      <c r="F74" s="8" t="n">
         <v>444.87</v>
       </c>
-      <c r="G74" s="16" t="n">
+      <c r="G74" s="8" t="n">
         <v>2669.2</v>
       </c>
     </row>
     <row r="75" ht="15.05" customHeight="1">
-      <c r="A75" s="14" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>AXIMA</t>
         </is>
       </c>
-      <c r="B75" s="17" t="n">
+      <c r="B75" s="9" t="n">
         <v>45982</v>
       </c>
-      <c r="C75" s="14" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>8710262855</t>
         </is>
       </c>
-      <c r="D75" s="14" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>ENTRETIEN PROTECTION INCENDIE</t>
         </is>
       </c>
-      <c r="E75" s="16" t="n">
+      <c r="E75" s="8" t="n">
         <v>2224.33</v>
       </c>
-      <c r="F75" s="16" t="n">
+      <c r="F75" s="8" t="n">
         <v>444.87</v>
       </c>
-      <c r="G75" s="16" t="n">
+      <c r="G75" s="8" t="n">
         <v>2669.2</v>
       </c>
     </row>
     <row r="76" ht="15.05" customHeight="1">
-      <c r="A76" s="14" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>AXIMA</t>
         </is>
       </c>
-      <c r="B76" s="17" t="n">
+      <c r="B76" s="9" t="n">
         <v>46012</v>
       </c>
-      <c r="C76" s="14" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t>8710264942</t>
         </is>
       </c>
-      <c r="D76" s="14" t="inlineStr">
+      <c r="D76" s="6" t="inlineStr">
         <is>
           <t>CONTRAT D’ENTRETIEN DE PROTECTION INCENDIE du 21/12/25 au 20/01/26</t>
         </is>
       </c>
-      <c r="E76" s="16" t="n">
+      <c r="E76" s="8" t="n">
         <v>2224.33</v>
       </c>
-      <c r="F76" s="16" t="n">
+      <c r="F76" s="8" t="n">
         <v>444.87</v>
       </c>
-      <c r="G76" s="16" t="n">
+      <c r="G76" s="8" t="n">
         <v>2669.2</v>
       </c>
     </row>
     <row r="77" ht="15.8" customHeight="1">
-      <c r="A77" s="18" t="inlineStr">
+      <c r="A77" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    Sous-total — SPK / RIA / PI</t>
         </is>
       </c>
-      <c r="E77" s="19">
+      <c r="E77" s="11">
         <f>SUM(E66:E76)</f>
         <v/>
       </c>
-      <c r="F77" s="19">
+      <c r="F77" s="11">
         <f>SUM(F66:F76)</f>
         <v/>
       </c>
-      <c r="G77" s="19">
+      <c r="G77" s="11">
         <f>SUM(G66:G76)</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Installations électriques</t>
         </is>
       </c>
     </row>
     <row r="79" ht="15.05" customHeight="1">
-      <c r="A79" s="14" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>OTIS</t>
         </is>
       </c>
-      <c r="B79" s="17" t="n">
+      <c r="B79" s="9" t="n">
         <v>45833</v>
       </c>
-      <c r="C79" s="14" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t>VOF 8192916</t>
         </is>
       </c>
-      <c r="D79" s="14" t="inlineStr">
+      <c r="D79" s="6" t="inlineStr">
         <is>
           <t>MAINTENANCE ASCENSEURS MAI JUIN 25</t>
         </is>
       </c>
-      <c r="E79" s="16" t="n">
+      <c r="E79" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="F79" s="16" t="n">
+      <c r="F79" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G79" s="16" t="n">
+      <c r="G79" s="8" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="80" ht="15.05" customHeight="1">
-      <c r="A80" s="14" t="inlineStr">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>OTIS</t>
         </is>
       </c>
-      <c r="B80" s="17" t="n">
+      <c r="B80" s="9" t="n">
         <v>45841</v>
       </c>
-      <c r="C80" s="14" t="inlineStr">
+      <c r="C80" s="6" t="inlineStr">
         <is>
           <t>VOF 8251287</t>
         </is>
       </c>
-      <c r="D80" s="14" t="inlineStr">
+      <c r="D80" s="6" t="inlineStr">
         <is>
           <t>MAINTENANCE ASCENSEURS T3</t>
         </is>
       </c>
-      <c r="E80" s="16" t="n">
+      <c r="E80" s="8" t="n">
         <v>750</v>
       </c>
-      <c r="F80" s="16" t="n">
+      <c r="F80" s="8" t="n">
         <v>150</v>
       </c>
-      <c r="G80" s="16" t="n">
+      <c r="G80" s="8" t="n">
         <v>900</v>
       </c>
     </row>
     <row r="81" ht="15.05" customHeight="1">
-      <c r="A81" s="14" t="inlineStr">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>EIFFAGE</t>
         </is>
       </c>
-      <c r="B81" s="17" t="n">
+      <c r="B81" s="9" t="n">
         <v>45833</v>
       </c>
-      <c r="C81" s="14" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>F00190250600306</t>
         </is>
       </c>
-      <c r="D81" s="14" t="inlineStr">
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>Maintenance électricité</t>
         </is>
       </c>
-      <c r="E81" s="16" t="n">
+      <c r="E81" s="8" t="n">
         <v>4700</v>
       </c>
-      <c r="F81" s="16" t="n">
+      <c r="F81" s="8" t="n">
         <v>940</v>
       </c>
-      <c r="G81" s="16" t="n">
+      <c r="G81" s="8" t="n">
         <v>5640</v>
       </c>
     </row>
     <row r="82" ht="15.05" customHeight="1">
-      <c r="A82" s="14" t="inlineStr">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>OTIS</t>
         </is>
       </c>
-      <c r="B82" s="17" t="n">
+      <c r="B82" s="9" t="n">
         <v>45932</v>
       </c>
-      <c r="C82" s="14" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
         <is>
           <t>VOF 8380322</t>
         </is>
       </c>
-      <c r="D82" s="14" t="inlineStr">
+      <c r="D82" s="6" t="inlineStr">
         <is>
           <t>Prestations de services Entretien du 01/10/25 au 31/12/25-Ascenceur</t>
         </is>
       </c>
-      <c r="E82" s="16" t="n">
+      <c r="E82" s="8" t="n">
         <v>750</v>
       </c>
-      <c r="F82" s="16" t="n">
+      <c r="F82" s="8" t="n">
         <v>150</v>
       </c>
-      <c r="G82" s="16" t="n">
+      <c r="G82" s="8" t="n">
         <v>900</v>
       </c>
     </row>
     <row r="83" ht="15.8" customHeight="1">
-      <c r="A83" s="18" t="inlineStr">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    Sous-total — Installations électriques</t>
         </is>
       </c>
-      <c r="E83" s="19">
+      <c r="E83" s="11">
         <f>SUM(E79:E82)</f>
         <v/>
       </c>
-      <c r="F83" s="19">
+      <c r="F83" s="11">
         <f>SUM(F79:F82)</f>
         <v/>
       </c>
-      <c r="G83" s="19">
+      <c r="G83" s="11">
         <f>SUM(G79:G82)</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Protection Foudre</t>
         </is>
       </c>
     </row>
     <row r="85" ht="15.05" customHeight="1">
-      <c r="A85" s="14" t="inlineStr">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>Etablissement Renard</t>
         </is>
       </c>
-      <c r="B85" s="17" t="n">
+      <c r="B85" s="9" t="n">
         <v>46006</v>
       </c>
-      <c r="C85" s="14" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>2512205</t>
         </is>
       </c>
-      <c r="D85" s="14" t="inlineStr">
+      <c r="D85" s="6" t="inlineStr">
         <is>
           <t>Contrat de vérification-maintenance protection contre la foudre</t>
         </is>
       </c>
-      <c r="E85" s="16" t="n">
+      <c r="E85" s="8" t="n">
         <v>1920</v>
       </c>
-      <c r="F85" s="16" t="n">
+      <c r="F85" s="8" t="n">
         <v>384</v>
       </c>
-      <c r="G85" s="16" t="n">
+      <c r="G85" s="8" t="n">
         <v>2304</v>
       </c>
     </row>
     <row r="86" ht="15.05" customHeight="1">
-      <c r="A86" s="14" t="inlineStr">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>BUREAU VERITAS</t>
         </is>
       </c>
-      <c r="B86" s="15" t="n"/>
-      <c r="C86" s="14" t="inlineStr"/>
-      <c r="D86" s="14" t="inlineStr"/>
-      <c r="E86" s="16" t="n">
+      <c r="B86" s="7" t="n"/>
+      <c r="C86" s="6" t="inlineStr"/>
+      <c r="D86" s="6" t="inlineStr"/>
+      <c r="E86" s="8" t="n">
         <v>695</v>
       </c>
-      <c r="F86" s="16" t="n">
+      <c r="F86" s="8" t="n">
         <v>139</v>
       </c>
-      <c r="G86" s="16" t="n">
+      <c r="G86" s="8" t="n">
         <v>834</v>
       </c>
     </row>
     <row r="87" ht="15.05" customHeight="1">
-      <c r="A87" s="14" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>BUREAU VERITAS</t>
         </is>
       </c>
-      <c r="B87" s="17" t="n">
+      <c r="B87" s="9" t="n">
         <v>45918</v>
       </c>
-      <c r="C87" s="14" t="inlineStr">
+      <c r="C87" s="6" t="inlineStr">
         <is>
           <t>25546933</t>
         </is>
       </c>
-      <c r="D87" s="14" t="inlineStr">
+      <c r="D87" s="6" t="inlineStr">
         <is>
           <t>Vérification périodique des installations électriques (Q19)</t>
         </is>
       </c>
-      <c r="E87" s="16" t="n">
+      <c r="E87" s="8" t="n">
         <v>695</v>
       </c>
-      <c r="F87" s="16" t="n">
+      <c r="F87" s="8" t="n">
         <v>139</v>
       </c>
-      <c r="G87" s="16" t="n">
+      <c r="G87" s="8" t="n">
         <v>834</v>
       </c>
     </row>
     <row r="88" ht="15.8" customHeight="1">
-      <c r="A88" s="18" t="inlineStr">
+      <c r="A88" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    Sous-total — Protection Foudre</t>
         </is>
       </c>
-      <c r="E88" s="19">
+      <c r="E88" s="11">
         <f>SUM(E85:E87)</f>
         <v/>
       </c>
-      <c r="F88" s="19">
+      <c r="F88" s="11">
         <f>SUM(F85:F87)</f>
         <v/>
       </c>
-      <c r="G88" s="19">
+      <c r="G88" s="11">
         <f>SUM(G85:G87)</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  GTB</t>
         </is>
       </c>
     </row>
     <row r="90" ht="15.05" customHeight="1">
-      <c r="A90" s="14" t="inlineStr">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>CN 45</t>
         </is>
       </c>
-      <c r="B90" s="15" t="n"/>
-      <c r="C90" s="14" t="inlineStr"/>
-      <c r="D90" s="14" t="inlineStr"/>
-      <c r="E90" s="16" t="n">
+      <c r="B90" s="7" t="n"/>
+      <c r="C90" s="6" t="inlineStr"/>
+      <c r="D90" s="6" t="inlineStr"/>
+      <c r="E90" s="8" t="n">
         <v>514</v>
       </c>
-      <c r="F90" s="16" t="n">
+      <c r="F90" s="8" t="n">
         <v>102.8</v>
       </c>
-      <c r="G90" s="16" t="n">
+      <c r="G90" s="8" t="n">
         <v>616.8</v>
       </c>
     </row>
     <row r="91" ht="15.05" customHeight="1">
-      <c r="A91" s="14" t="inlineStr">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>CN 45</t>
         </is>
       </c>
-      <c r="B91" s="17" t="n">
+      <c r="B91" s="9" t="n">
         <v>45835</v>
       </c>
-      <c r="C91" s="14" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>2025/754</t>
         </is>
       </c>
-      <c r="D91" s="14" t="inlineStr"/>
-      <c r="E91" s="16" t="n">
+      <c r="D91" s="6" t="inlineStr"/>
+      <c r="E91" s="8" t="n">
         <v>514</v>
       </c>
-      <c r="F91" s="16" t="n">
+      <c r="F91" s="8" t="n">
         <v>102.8</v>
       </c>
-      <c r="G91" s="16" t="n">
+      <c r="G91" s="8" t="n">
         <v>616.8</v>
       </c>
     </row>
     <row r="92" ht="15.05" customHeight="1">
-      <c r="A92" s="14" t="inlineStr">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>SOA</t>
         </is>
       </c>
-      <c r="B92" s="15" t="n"/>
-      <c r="C92" s="14" t="inlineStr"/>
-      <c r="D92" s="14" t="inlineStr"/>
-      <c r="E92" s="16" t="n">
+      <c r="B92" s="7" t="n"/>
+      <c r="C92" s="6" t="inlineStr"/>
+      <c r="D92" s="6" t="inlineStr"/>
+      <c r="E92" s="8" t="n">
         <v>2577</v>
       </c>
-      <c r="F92" s="16" t="n">
+      <c r="F92" s="8" t="n">
         <v>515.4</v>
       </c>
-      <c r="G92" s="16" t="n">
+      <c r="G92" s="8" t="n">
         <v>3092.4</v>
       </c>
     </row>
     <row r="93" ht="15.05" customHeight="1">
-      <c r="A93" s="14" t="inlineStr">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>SOA</t>
         </is>
       </c>
-      <c r="B93" s="17" t="n">
+      <c r="B93" s="9" t="n">
         <v>45956</v>
       </c>
-      <c r="C93" s="14" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>251003937</t>
         </is>
       </c>
-      <c r="D93" s="14" t="inlineStr">
+      <c r="D93" s="6" t="inlineStr">
         <is>
           <t>Entretien des séparateurs hydrocarbures</t>
         </is>
       </c>
-      <c r="E93" s="16" t="n">
+      <c r="E93" s="8" t="n">
         <v>2577</v>
       </c>
-      <c r="F93" s="16" t="n">
+      <c r="F93" s="8" t="n">
         <v>515.4</v>
       </c>
-      <c r="G93" s="16" t="n">
+      <c r="G93" s="8" t="n">
         <v>3092.4</v>
       </c>
     </row>
     <row r="94" ht="15.05" customHeight="1">
-      <c r="A94" s="14" t="inlineStr">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t>NEO DB / B27 / BUREAU VERITAS</t>
         </is>
       </c>
-      <c r="B94" s="15" t="n"/>
-      <c r="C94" s="14" t="inlineStr"/>
-      <c r="D94" s="14" t="inlineStr"/>
-      <c r="E94" s="16" t="n">
+      <c r="B94" s="7" t="n"/>
+      <c r="C94" s="6" t="inlineStr"/>
+      <c r="D94" s="6" t="inlineStr"/>
+      <c r="E94" s="8" t="n">
         <v>1602.5</v>
       </c>
-      <c r="F94" s="16" t="n">
+      <c r="F94" s="8" t="n">
         <v>320.5</v>
       </c>
-      <c r="G94" s="16" t="n">
+      <c r="G94" s="8" t="n">
         <v>1923</v>
       </c>
     </row>
     <row r="95" ht="15.05" customHeight="1">
-      <c r="A95" s="14" t="inlineStr">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t>BUREAU VERITAS</t>
         </is>
       </c>
-      <c r="B95" s="17" t="n">
+      <c r="B95" s="9" t="n">
         <v>45859</v>
       </c>
-      <c r="C95" s="14" t="inlineStr">
+      <c r="C95" s="6" t="inlineStr">
         <is>
           <t>25425847</t>
         </is>
       </c>
-      <c r="D95" s="14" t="inlineStr">
+      <c r="D95" s="6" t="inlineStr">
         <is>
           <t>CONTRÔLE REJETS CHAUFFERIE ET REJETS ACQUEUX</t>
         </is>
       </c>
-      <c r="E95" s="16" t="n">
+      <c r="E95" s="8" t="n">
         <v>1147.5</v>
       </c>
-      <c r="F95" s="16" t="n">
+      <c r="F95" s="8" t="n">
         <v>229.5</v>
       </c>
-      <c r="G95" s="16" t="n">
+      <c r="G95" s="8" t="n">
         <v>1377</v>
       </c>
     </row>
     <row r="96" ht="15.05" customHeight="1">
-      <c r="A96" s="14" t="inlineStr">
+      <c r="A96" s="6" t="inlineStr">
         <is>
           <t>BUREAU VERITAS</t>
         </is>
       </c>
-      <c r="B96" s="17" t="n">
+      <c r="B96" s="9" t="n">
         <v>45918</v>
       </c>
-      <c r="C96" s="14" t="inlineStr"/>
-      <c r="D96" s="14" t="inlineStr">
+      <c r="C96" s="6" t="inlineStr"/>
+      <c r="D96" s="6" t="inlineStr">
         <is>
           <t>Vérification périodique des disconnecteurs</t>
         </is>
       </c>
-      <c r="E96" s="16" t="n">
+      <c r="E96" s="8" t="n">
         <v>455</v>
       </c>
-      <c r="F96" s="16" t="n">
+      <c r="F96" s="8" t="n">
         <v>91</v>
       </c>
-      <c r="G96" s="16" t="n">
+      <c r="G96" s="8" t="n">
         <v>546</v>
       </c>
     </row>
     <row r="97" ht="15.8" customHeight="1">
-      <c r="A97" s="18" t="inlineStr">
+      <c r="A97" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    Sous-total — GTB</t>
         </is>
       </c>
-      <c r="E97" s="19">
+      <c r="E97" s="11">
         <f>SUM(E90:E96)</f>
         <v/>
       </c>
-      <c r="F97" s="19">
+      <c r="F97" s="11">
         <f>SUM(F90:F96)</f>
         <v/>
       </c>
-      <c r="G97" s="19">
+      <c r="G97" s="11">
         <f>SUM(G90:G96)</f>
         <v/>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Détection Gaz</t>
         </is>
       </c>
     </row>
     <row r="99" ht="15.05" customHeight="1">
-      <c r="A99" s="14" t="inlineStr">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>BE ATEX</t>
         </is>
       </c>
-      <c r="B99" s="15" t="n"/>
-      <c r="C99" s="14" t="inlineStr">
+      <c r="B99" s="7" t="n"/>
+      <c r="C99" s="6" t="inlineStr">
         <is>
           <t>CC65197</t>
         </is>
       </c>
-      <c r="D99" s="14" t="inlineStr">
+      <c r="D99" s="6" t="inlineStr">
         <is>
           <t>CONTRÔLE ET VERIFICATION DES EQUIPEMENTS DE DETECTION GAZ FIXES</t>
         </is>
       </c>
-      <c r="E99" s="16" t="n">
+      <c r="E99" s="8" t="n">
         <v>344.96</v>
       </c>
-      <c r="F99" s="16" t="n">
+      <c r="F99" s="8" t="n">
         <v>68.98999999999999</v>
       </c>
-      <c r="G99" s="16" t="n">
+      <c r="G99" s="8" t="n">
         <v>413.95</v>
       </c>
     </row>
     <row r="100" ht="15.05" customHeight="1">
-      <c r="A100" s="14" t="inlineStr">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>BE ATEX</t>
         </is>
       </c>
-      <c r="B100" s="17" t="n">
+      <c r="B100" s="9" t="n">
         <v>45974</v>
       </c>
-      <c r="C100" s="14" t="inlineStr">
+      <c r="C100" s="6" t="inlineStr">
         <is>
           <t>FC76885</t>
         </is>
       </c>
-      <c r="D100" s="14" t="inlineStr">
+      <c r="D100" s="6" t="inlineStr">
         <is>
           <t>CONTRÔLE ET VERIFICATION DES EQUIPEMENTS DE DETECTION GAZ FIXES</t>
         </is>
       </c>
-      <c r="E100" s="16" t="n">
+      <c r="E100" s="8" t="n">
         <v>344.96</v>
       </c>
-      <c r="F100" s="16" t="n">
+      <c r="F100" s="8" t="n">
         <v>68.98999999999999</v>
       </c>
-      <c r="G100" s="16" t="n">
+      <c r="G100" s="8" t="n">
         <v>413.95</v>
       </c>
     </row>
     <row r="101" ht="15.8" customHeight="1">
-      <c r="A101" s="18" t="inlineStr">
+      <c r="A101" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    Sous-total — Détection Gaz</t>
         </is>
       </c>
-      <c r="E101" s="19">
+      <c r="E101" s="11">
         <f>SUM(E99:E100)</f>
         <v/>
       </c>
-      <c r="F101" s="19">
+      <c r="F101" s="11">
         <f>SUM(F99:F100)</f>
         <v/>
       </c>
-      <c r="G101" s="19">
+      <c r="G101" s="11">
         <f>SUM(G99:G100)</f>
         <v/>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="A102" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Vérifications règlementaires</t>
         </is>
       </c>
     </row>
     <row r="103" ht="13.5" customHeight="1">
-      <c r="D103" s="20" t="inlineStr">
+      <c r="D103" s="12" t="inlineStr">
         <is>
           <t>— Aucune facture —</t>
         </is>
       </c>
     </row>
     <row r="104" ht="15.8" customHeight="1">
-      <c r="A104" s="18" t="inlineStr">
+      <c r="A104" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    Sous-total — Vérifications règlementaires</t>
         </is>
       </c>
-      <c r="E104" s="19" t="n">
+      <c r="E104" s="11" t="n">
         <v>667.0599999999999</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="A105" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Portails</t>
         </is>
       </c>
     </row>
     <row r="106" ht="15.05" customHeight="1">
-      <c r="A106" s="14" t="inlineStr">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>SGC FERMETURE</t>
         </is>
       </c>
-      <c r="B106" s="17" t="n">
+      <c r="B106" s="9" t="n">
         <v>45867</v>
       </c>
-      <c r="C106" s="14" t="inlineStr">
+      <c r="C106" s="6" t="inlineStr">
         <is>
           <t>2994</t>
         </is>
       </c>
-      <c r="D106" s="14" t="inlineStr">
+      <c r="D106" s="6" t="inlineStr">
         <is>
           <t>ENTRETIEN PORTAILS ET BARRIERES</t>
         </is>
       </c>
-      <c r="E106" s="16" t="n">
+      <c r="E106" s="8" t="n">
         <v>333.53</v>
       </c>
-      <c r="F106" s="16" t="n">
+      <c r="F106" s="8" t="n">
         <v>66.70999999999999</v>
       </c>
-      <c r="G106" s="16" t="n">
+      <c r="G106" s="8" t="n">
         <v>400.24</v>
       </c>
     </row>
     <row r="107" ht="15.8" customHeight="1">
-      <c r="A107" s="18" t="inlineStr">
+      <c r="A107" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    Sous-total — Portails</t>
         </is>
       </c>
-      <c r="E107" s="19">
+      <c r="E107" s="11">
         <f>SUM(E106:E106)</f>
         <v/>
       </c>
-      <c r="F107" s="19">
+      <c r="F107" s="11">
         <f>SUM(F106:F106)</f>
         <v/>
       </c>
-      <c r="G107" s="19">
+      <c r="G107" s="11">
         <f>SUM(G106:G106)</f>
         <v/>
       </c>
     </row>
     <row r="108" ht="21.75" customHeight="1">
-      <c r="A108" s="13" t="inlineStr">
+      <c r="A108" s="4" t="inlineStr">
         <is>
           <t>── ASSURANCES + JURIDIQUE ──</t>
         </is>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="A109" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Assurances</t>
         </is>
       </c>
     </row>
     <row r="110" ht="15.05" customHeight="1">
-      <c r="A110" s="14" t="inlineStr">
+      <c r="A110" s="6" t="inlineStr">
         <is>
           <t>WTW</t>
         </is>
       </c>
-      <c r="B110" s="17" t="n">
+      <c r="B110" s="9" t="n">
         <v>45799</v>
       </c>
-      <c r="C110" s="14" t="inlineStr"/>
-      <c r="D110" s="14" t="inlineStr">
+      <c r="C110" s="6" t="inlineStr"/>
+      <c r="D110" s="6" t="inlineStr">
         <is>
           <t>BATIMENT A / 'Du 30 mai 2025 au 29 mai 2026</t>
         </is>
       </c>
-      <c r="E110" s="16" t="n">
+      <c r="E110" s="8" t="n">
         <v>40320.47</v>
       </c>
-      <c r="F110" s="15" t="n"/>
-      <c r="G110" s="16" t="n">
+      <c r="F110" s="13" t="n"/>
+      <c r="G110" s="8" t="n">
         <v>40320.47</v>
       </c>
     </row>
     <row r="111" ht="15.8" customHeight="1">
-      <c r="A111" s="18" t="inlineStr">
+      <c r="A111" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    Sous-total — Assurances</t>
         </is>
       </c>
-      <c r="E111" s="19">
+      <c r="E111" s="11">
         <f>SUM(E110:E110)</f>
         <v/>
       </c>
-      <c r="F111" s="19">
+      <c r="F111" s="11">
         <f>SUM(F110:F110)</f>
         <v/>
       </c>
-      <c r="G111" s="19">
+      <c r="G111" s="11">
         <f>SUM(G110:G110)</f>
         <v/>
       </c>
     </row>
     <row r="112" ht="21.75" customHeight="1">
-      <c r="A112" s="13" t="inlineStr">
+      <c r="A112" s="4" t="inlineStr">
         <is>
           <t>── CHARGES NON RECUPERABLES ──</t>
         </is>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="A113" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Frais Bancaires</t>
         </is>
       </c>
     </row>
     <row r="114" ht="15.05" customHeight="1">
-      <c r="A114" s="14" t="inlineStr">
+      <c r="A114" s="6" t="inlineStr">
         <is>
           <t>Caisse d'épargne</t>
         </is>
       </c>
-      <c r="B114" s="17" t="n">
+      <c r="B114" s="9" t="n">
         <v>45839</v>
       </c>
-      <c r="C114" s="14" t="inlineStr"/>
-      <c r="D114" s="14" t="inlineStr">
+      <c r="C114" s="6" t="inlineStr"/>
+      <c r="D114" s="6" t="inlineStr">
         <is>
           <t>COMMISSIONS</t>
         </is>
       </c>
-      <c r="E114" s="16" t="n">
+      <c r="E114" s="8" t="n">
         <v>55.77</v>
       </c>
-      <c r="F114" s="15" t="n"/>
-      <c r="G114" s="16" t="n">
+      <c r="F114" s="13" t="n"/>
+      <c r="G114" s="8" t="n">
         <v>55.77</v>
       </c>
     </row>
     <row r="115" ht="15.05" customHeight="1">
-      <c r="A115" s="14" t="inlineStr">
+      <c r="A115" s="6" t="inlineStr">
         <is>
           <t>Caisse d'épargne</t>
         </is>
       </c>
-      <c r="B115" s="17" t="n">
+      <c r="B115" s="9" t="n">
         <v>45848</v>
       </c>
-      <c r="C115" s="14" t="inlineStr"/>
-      <c r="D115" s="14" t="inlineStr">
+      <c r="C115" s="6" t="inlineStr"/>
+      <c r="D115" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">FORFAIT LIBRE DE CONVERGENCE </t>
         </is>
       </c>
-      <c r="E115" s="16" t="n">
+      <c r="E115" s="8" t="n">
         <v>75.3</v>
       </c>
-      <c r="F115" s="15" t="n"/>
-      <c r="G115" s="16" t="n">
+      <c r="F115" s="13" t="n"/>
+      <c r="G115" s="8" t="n">
         <v>75.3</v>
       </c>
     </row>
     <row r="116" ht="15.05" customHeight="1">
-      <c r="A116" s="14" t="inlineStr">
+      <c r="A116" s="6" t="inlineStr">
         <is>
           <t>Caisse d'épargne</t>
         </is>
       </c>
-      <c r="B116" s="17" t="n">
+      <c r="B116" s="9" t="n">
         <v>45931</v>
       </c>
-      <c r="C116" s="14" t="inlineStr"/>
-      <c r="D116" s="14" t="inlineStr">
+      <c r="C116" s="6" t="inlineStr"/>
+      <c r="D116" s="6" t="inlineStr">
         <is>
           <t>COMMISSIONS</t>
         </is>
       </c>
-      <c r="E116" s="16" t="n">
+      <c r="E116" s="8" t="n">
         <v>86.38</v>
       </c>
-      <c r="F116" s="15" t="n"/>
-      <c r="G116" s="16" t="n">
+      <c r="F116" s="13" t="n"/>
+      <c r="G116" s="8" t="n">
         <v>86.38</v>
       </c>
     </row>
     <row r="117" ht="15.05" customHeight="1">
-      <c r="A117" s="14" t="inlineStr">
+      <c r="A117" s="6" t="inlineStr">
         <is>
           <t>Caisse d'épargne</t>
         </is>
       </c>
-      <c r="B117" s="17" t="n">
+      <c r="B117" s="9" t="n">
         <v>45939</v>
       </c>
-      <c r="C117" s="14" t="inlineStr"/>
-      <c r="D117" s="14" t="inlineStr">
+      <c r="C117" s="6" t="inlineStr"/>
+      <c r="D117" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">FORFAIT LIBRE DE CONVERGENCE </t>
         </is>
       </c>
-      <c r="E117" s="16" t="n">
+      <c r="E117" s="8" t="n">
         <v>75.3</v>
       </c>
-      <c r="F117" s="15" t="n"/>
-      <c r="G117" s="16" t="n">
+      <c r="F117" s="13" t="n"/>
+      <c r="G117" s="8" t="n">
         <v>75.3</v>
       </c>
     </row>
     <row r="118" ht="15.8" customHeight="1">
-      <c r="A118" s="18" t="inlineStr">
+      <c r="A118" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    Sous-total — Frais Bancaires</t>
         </is>
       </c>
-      <c r="E118" s="19">
+      <c r="E118" s="11">
         <f>SUM(E114:E117)</f>
         <v/>
       </c>
-      <c r="F118" s="19">
+      <c r="F118" s="11">
         <f>SUM(F114:F117)</f>
         <v/>
       </c>
-      <c r="G118" s="19">
+      <c r="G118" s="11">
         <f>SUM(G114:G117)</f>
         <v/>
       </c>
@@ -3399,13 +3280,190 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ORMES A — PARAMÈTRES SITE 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.8" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>ORMES A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.8" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Surface totale site (m²)</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>29565.91</v>
+      </c>
+    </row>
+    <row r="4" ht="15.8" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Année</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="5" ht="7.55" customHeight="1"/>
+    <row r="6" ht="19.55" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Surface (m²)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Bâtiment</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Locataire</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Début de bail / MAD</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Fin de bail</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Jours 2025</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Prorata</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.05" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>C1 C2</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Occupé</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>9623</v>
+      </c>
+      <c r="D7" s="17" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>ID LOGISTICS</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>45737</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>50119</v>
+      </c>
+      <c r="H7" s="20">
+        <f>MAX(0,MIN(DATE(2025,12,31),IF(G7&gt;0,G7,DATE(2025,12,31)))-MAX(DATE(2025,1,1),IF(F7&gt;0,F7,DATE(2025,1,1)))+1)</f>
+        <v/>
+      </c>
+      <c r="I7" s="21">
+        <f>H7/365</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15.05" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>C3 C4 C5</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>Vacant</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>19942.91</v>
+      </c>
+      <c r="D8" s="17" t="inlineStr"/>
+      <c r="E8" s="18" t="inlineStr"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="17" t="n"/>
+      <c r="H8" s="20">
+        <f>MAX(0,MIN(DATE(2025,12,31),IF(G8&gt;0,G8,DATE(2025,12,31)))-MAX(DATE(2025,1,1),IF(F8&gt;0,F8,DATE(2025,1,1)))+1)</f>
+        <v/>
+      </c>
+      <c r="I8" s="21">
+        <f>H8/365</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3416,742 +3474,1730 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.55" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>RÉGULARISATION DE CHARGES — C1 C2</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.8" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Site : ORMES A  |  Année 2025  |  Lot : C1 C2  |  Surface lot C1 C2 : 9623.0 m²  |  </t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Site : ORMES A  |  Année 2025</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.8" customHeight="1">
-      <c r="A3" s="12">
+      <c r="A3" s="2">
         <f>Paramètres!$B$7&amp;IF(Paramètres!$E$7&lt;&gt;""," — "&amp;Paramètres!$E$7,"")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="19.55" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Poste</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Clé répartition</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Total site HT</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>QP annuelle</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Période</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>QP locataire</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>FLUIDES</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15.05" customHeight="1">
-      <c r="A6" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Eau</t>
-        </is>
-      </c>
-      <c r="B6" s="23">
-        <f>(Paramètres!$C$7/Paramètres!$C$3)</f>
-        <v/>
-      </c>
-      <c r="C6" s="24">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>Eau</t>
+        </is>
+      </c>
+      <c r="B6" s="25">
+        <f>Paramètres!$C$7/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C6" s="26">
         <f>'Récapitulatif 2025'!E10</f>
         <v/>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="26">
         <f>B6*C6</f>
         <v/>
       </c>
-      <c r="E6" s="25">
-        <f>MAX(0,MIN(DATE(2025,12,31),IF(Paramètres!$I$7&gt;0,Paramètres!$I$7,DATE(2025,12,31)))-MAX(DATE(2025,1,1),IF(Paramètres!$H$7&gt;0,Paramètres!$H$7,DATE(2025,1,1)))+1)/365</f>
-        <v/>
-      </c>
-      <c r="F6" s="24">
+      <c r="E6" s="27">
+        <f>Paramètres!$H$7/365</f>
+        <v/>
+      </c>
+      <c r="F6" s="26">
         <f>D6*E6</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15.05" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Electricité</t>
-        </is>
-      </c>
-      <c r="B7" s="23">
-        <f>(Paramètres!$C$7/Paramètres!$C$3)</f>
-        <v/>
-      </c>
-      <c r="C7" s="24">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>Electricité</t>
+        </is>
+      </c>
+      <c r="B7" s="25">
+        <f>Paramètres!$C$7/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C7" s="26">
         <f>'Récapitulatif 2025'!E21</f>
         <v/>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="26">
         <f>B7*C7</f>
         <v/>
       </c>
-      <c r="E7" s="25">
-        <f>MAX(0,MIN(DATE(2025,12,31),IF(Paramètres!$I$7&gt;0,Paramètres!$I$7,DATE(2025,12,31)))-MAX(DATE(2025,1,1),IF(Paramètres!$H$7&gt;0,Paramètres!$H$7,DATE(2025,1,1)))+1)/365</f>
-        <v/>
-      </c>
-      <c r="F7" s="24">
+      <c r="E7" s="27">
+        <f>Paramètres!$H$7/365</f>
+        <v/>
+      </c>
+      <c r="F7" s="26">
         <f>D7*E7</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15.05" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Gaz</t>
-        </is>
-      </c>
-      <c r="B8" s="23">
-        <f>(Paramètres!$C$7/Paramètres!$C$3)</f>
-        <v/>
-      </c>
-      <c r="C8" s="24">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>Gaz</t>
+        </is>
+      </c>
+      <c r="B8" s="25">
+        <f>Paramètres!$C$7/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C8" s="26">
         <f>'Récapitulatif 2025'!E32</f>
         <v/>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="26">
         <f>B8*C8</f>
         <v/>
       </c>
-      <c r="E8" s="25">
-        <f>MAX(0,MIN(DATE(2025,12,31),IF(Paramètres!$I$7&gt;0,Paramètres!$I$7,DATE(2025,12,31)))-MAX(DATE(2025,1,1),IF(Paramètres!$H$7&gt;0,Paramètres!$H$7,DATE(2025,1,1)))+1)/365</f>
-        <v/>
-      </c>
-      <c r="F8" s="24">
+      <c r="E8" s="27">
+        <f>Paramètres!$H$7/365</f>
+        <v/>
+      </c>
+      <c r="F8" s="26">
         <f>D8*E8</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Sous-total — FLUIDES</t>
+        </is>
+      </c>
+      <c r="C9" s="11">
+        <f>SUM(C6:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="11">
+        <f>SUM(D6:D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="28" t="n"/>
+      <c r="F9" s="11">
+        <f>SUM(F6:F8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>TRAVAUX</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15.05" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Entretien Courant</t>
-        </is>
-      </c>
-      <c r="B10" s="23">
-        <f>(Paramètres!$C$7/Paramètres!$C$3)</f>
-        <v/>
-      </c>
-      <c r="C10" s="24">
+    <row r="11" ht="15.05" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>Entretien Courant</t>
+        </is>
+      </c>
+      <c r="B11" s="25">
+        <f>Paramètres!$C$7/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C11" s="26">
         <f>'Récapitulatif 2025'!E37</f>
         <v/>
       </c>
-      <c r="D10" s="24">
-        <f>B10*C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="25">
-        <f>MAX(0,MIN(DATE(2025,12,31),IF(Paramètres!$I$7&gt;0,Paramètres!$I$7,DATE(2025,12,31)))-MAX(DATE(2025,1,1),IF(Paramètres!$F$7&gt;0,Paramètres!$F$7,DATE(2025,1,1)))+1)/365</f>
-        <v/>
-      </c>
-      <c r="F10" s="24">
-        <f>D10*E10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="D11" s="26">
+        <f>B11*C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="27">
+        <f>Paramètres!$H$7/365</f>
+        <v/>
+      </c>
+      <c r="F11" s="26">
+        <f>D11*E11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Sous-total — TRAVAUX</t>
+        </is>
+      </c>
+      <c r="C12" s="11">
+        <f>SUM(C11:C11)</f>
+        <v/>
+      </c>
+      <c r="D12" s="11">
+        <f>SUM(D11:D11)</f>
+        <v/>
+      </c>
+      <c r="E12" s="28" t="n"/>
+      <c r="F12" s="11">
+        <f>SUM(F11:F11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>CONTRAT MAINTENANCE</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15.05" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Espaces Verts</t>
-        </is>
-      </c>
-      <c r="B12" s="23">
-        <f>(Paramètres!$C$7/Paramètres!$C$3)</f>
-        <v/>
-      </c>
-      <c r="C12" s="24">
+    <row r="14" ht="15.05" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>Espaces Verts</t>
+        </is>
+      </c>
+      <c r="B14" s="25">
+        <f>Paramètres!$C$7/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C14" s="26">
         <f>'Récapitulatif 2025'!E46</f>
         <v/>
       </c>
-      <c r="D12" s="24">
-        <f>B12*C12</f>
-        <v/>
-      </c>
-      <c r="E12" s="25">
-        <f>MAX(0,MIN(DATE(2025,12,31),IF(Paramètres!$I$7&gt;0,Paramètres!$I$7,DATE(2025,12,31)))-MAX(DATE(2025,1,1),IF(Paramètres!$F$7&gt;0,Paramètres!$F$7,DATE(2025,1,1)))+1)/365</f>
-        <v/>
-      </c>
-      <c r="F12" s="24">
-        <f>D12*E12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15.05" customHeight="1">
-      <c r="A13" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CVC</t>
-        </is>
-      </c>
-      <c r="B13" s="23">
-        <f>(Paramètres!$C$7/Paramètres!$C$3)</f>
-        <v/>
-      </c>
-      <c r="C13" s="24">
+      <c r="D14" s="26">
+        <f>B14*C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="27">
+        <f>Paramètres!$H$7/365</f>
+        <v/>
+      </c>
+      <c r="F14" s="26">
+        <f>D14*E14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15.05" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="B15" s="25">
+        <f>Paramètres!$C$7/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C15" s="26">
         <f>'Récapitulatif 2025'!E50</f>
         <v/>
       </c>
-      <c r="D13" s="24">
-        <f>B13*C13</f>
-        <v/>
-      </c>
-      <c r="E13" s="25">
-        <f>MAX(0,MIN(DATE(2025,12,31),IF(Paramètres!$I$7&gt;0,Paramètres!$I$7,DATE(2025,12,31)))-MAX(DATE(2025,1,1),IF(Paramètres!$F$7&gt;0,Paramètres!$F$7,DATE(2025,1,1)))+1)/365</f>
-        <v/>
-      </c>
-      <c r="F13" s="24">
-        <f>D13*E13</f>
-        <v/>
+      <c r="D15" s="26">
+        <f>B15*C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="27">
+        <f>Paramètres!$H$7/365</f>
+        <v/>
+      </c>
+      <c r="F15" s="26">
+        <f>D15*E15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.05" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>Sécurité</t>
+        </is>
+      </c>
+      <c r="B16" s="25">
+        <f>Paramètres!$C$7/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C16" s="26">
+        <f>'Récapitulatif 2025'!E54</f>
+        <v/>
+      </c>
+      <c r="D16" s="26">
+        <f>B16*C16</f>
+        <v/>
+      </c>
+      <c r="E16" s="27">
+        <f>Paramètres!$H$7/365</f>
+        <v/>
+      </c>
+      <c r="F16" s="26">
+        <f>D16*E16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.05" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>SSI</t>
+        </is>
+      </c>
+      <c r="B17" s="25">
+        <f>Paramètres!$C$7/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C17" s="26">
+        <f>'Récapitulatif 2025'!E59</f>
+        <v/>
+      </c>
+      <c r="D17" s="26">
+        <f>B17*C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="27">
+        <f>Paramètres!$H$7/365</f>
+        <v/>
+      </c>
+      <c r="F17" s="26">
+        <f>D17*E17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15.05" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>Toitures</t>
+        </is>
+      </c>
+      <c r="B18" s="25">
+        <f>Paramètres!$C$7/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C18" s="26">
+        <f>'Récapitulatif 2025'!E64</f>
+        <v/>
+      </c>
+      <c r="D18" s="26">
+        <f>B18*C18</f>
+        <v/>
+      </c>
+      <c r="E18" s="27">
+        <f>Paramètres!$H$7/365</f>
+        <v/>
+      </c>
+      <c r="F18" s="26">
+        <f>D18*E18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15.05" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>SPK / RIA / PI</t>
+        </is>
+      </c>
+      <c r="B19" s="25">
+        <f>Paramètres!$C$7/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C19" s="26">
+        <f>'Récapitulatif 2025'!E77</f>
+        <v/>
+      </c>
+      <c r="D19" s="26">
+        <f>B19*C19</f>
+        <v/>
+      </c>
+      <c r="E19" s="27">
+        <f>Paramètres!$H$7/365</f>
+        <v/>
+      </c>
+      <c r="F19" s="26">
+        <f>D19*E19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15.05" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>Installations électriques</t>
+        </is>
+      </c>
+      <c r="B20" s="25">
+        <f>Paramètres!$C$7/35730.0</f>
+        <v/>
+      </c>
+      <c r="C20" s="26">
+        <f>'Récapitulatif 2025'!E83</f>
+        <v/>
+      </c>
+      <c r="D20" s="26">
+        <f>B20*C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="27">
+        <f>Paramètres!$H$7/365</f>
+        <v/>
+      </c>
+      <c r="F20" s="26">
+        <f>D20*E20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15.05" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>Protection Foudre</t>
+        </is>
+      </c>
+      <c r="B21" s="25">
+        <f>Paramètres!$C$7/23820.0</f>
+        <v/>
+      </c>
+      <c r="C21" s="26">
+        <f>'Récapitulatif 2025'!E88</f>
+        <v/>
+      </c>
+      <c r="D21" s="26">
+        <f>B21*C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="27">
+        <f>Paramètres!$H$7/365</f>
+        <v/>
+      </c>
+      <c r="F21" s="26">
+        <f>D21*E21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15.05" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>GTB</t>
+        </is>
+      </c>
+      <c r="B22" s="25">
+        <f>Paramètres!$C$7/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C22" s="26">
+        <f>'Récapitulatif 2025'!E97</f>
+        <v/>
+      </c>
+      <c r="D22" s="26">
+        <f>B22*C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="27">
+        <f>Paramètres!$H$7/365</f>
+        <v/>
+      </c>
+      <c r="F22" s="26">
+        <f>D22*E22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15.05" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>Détection Gaz</t>
+        </is>
+      </c>
+      <c r="B23" s="25">
+        <f>Paramètres!$C$7/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C23" s="26">
+        <f>'Récapitulatif 2025'!E101</f>
+        <v/>
+      </c>
+      <c r="D23" s="26">
+        <f>B23*C23</f>
+        <v/>
+      </c>
+      <c r="E23" s="27">
+        <f>Paramètres!$H$7/365</f>
+        <v/>
+      </c>
+      <c r="F23" s="26">
+        <f>D23*E23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15.05" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>Vérifications règlementaires</t>
+        </is>
+      </c>
+      <c r="B24" s="25">
+        <f>Paramètres!$C$7/19945.0</f>
+        <v/>
+      </c>
+      <c r="C24" s="26">
+        <f>'Récapitulatif 2025'!E104</f>
+        <v/>
+      </c>
+      <c r="D24" s="26">
+        <f>B24*C24</f>
+        <v/>
+      </c>
+      <c r="E24" s="27">
+        <f>Paramètres!$H$7/365</f>
+        <v/>
+      </c>
+      <c r="F24" s="26">
+        <f>D24*E24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15.05" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Portails</t>
+        </is>
+      </c>
+      <c r="B25" s="25">
+        <f>Paramètres!$C$7/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C25" s="26">
+        <f>'Récapitulatif 2025'!E107</f>
+        <v/>
+      </c>
+      <c r="D25" s="26">
+        <f>B25*C25</f>
+        <v/>
+      </c>
+      <c r="E25" s="27">
+        <f>Paramètres!$H$7/365</f>
+        <v/>
+      </c>
+      <c r="F25" s="26">
+        <f>D25*E25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Sous-total — CONTRAT MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="C26" s="11">
+        <f>SUM(C14:C25)</f>
+        <v/>
+      </c>
+      <c r="D26" s="11">
+        <f>SUM(D14:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="28" t="n"/>
+      <c r="F26" s="11">
+        <f>SUM(F14:F25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>ASSURANCES + JURIDIQUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15.05" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Assurances</t>
+        </is>
+      </c>
+      <c r="B28" s="25">
+        <f>Paramètres!$C$7/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C28" s="26">
+        <f>'Récapitulatif 2025'!E111</f>
+        <v/>
+      </c>
+      <c r="D28" s="26">
+        <f>B28*C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="27">
+        <f>Paramètres!$H$7/365</f>
+        <v/>
+      </c>
+      <c r="F28" s="26">
+        <f>D28*E28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Sous-total — ASSURANCES + JURIDIQUE</t>
+        </is>
+      </c>
+      <c r="C29" s="11">
+        <f>SUM(C28:C28)</f>
+        <v/>
+      </c>
+      <c r="D29" s="11">
+        <f>SUM(D28:D28)</f>
+        <v/>
+      </c>
+      <c r="E29" s="28" t="n"/>
+      <c r="F29" s="11">
+        <f>SUM(F28:F28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="7.55" customHeight="1"/>
+    <row r="31" ht="21.75" customHeight="1">
+      <c r="A31" s="29" t="inlineStr">
+        <is>
+          <t>TOTAL CHARGES RÉCUPÉRABLES RÉELLES (€ HT)</t>
+        </is>
+      </c>
+      <c r="C31" s="30">
+        <f>C9+C12+C26+C29</f>
+        <v/>
+      </c>
+      <c r="D31" s="30">
+        <f>D9+D12+D26+D29</f>
+        <v/>
+      </c>
+      <c r="E31" s="31" t="n"/>
+      <c r="F31" s="30">
+        <f>F9+F12+F26+F29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="7.55" customHeight="1"/>
+    <row r="33" ht="19.55" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Provisions pour charges versées</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33" t="inlineStr">
+        <is>
+          <t>Montant annuel (€)</t>
+        </is>
+      </c>
+      <c r="E33" s="32" t="n"/>
+      <c r="F33" s="33" t="inlineStr">
+        <is>
+          <t>Montant locataire (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15.8" customHeight="1">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1er trimestre (T1)</t>
+        </is>
+      </c>
+      <c r="F34" s="26" t="n">
+        <v>2990.6</v>
+      </c>
+    </row>
+    <row r="35" ht="15.8" customHeight="1">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2e trimestre (T2)</t>
+        </is>
+      </c>
+      <c r="F35" s="26" t="n">
+        <v>25284.11</v>
+      </c>
+    </row>
+    <row r="36" ht="15.8" customHeight="1">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3e trimestre (T3)</t>
+        </is>
+      </c>
+      <c r="F36" s="26" t="n">
+        <v>28376.42</v>
+      </c>
+    </row>
+    <row r="37" ht="15.8" customHeight="1">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4e trimestre (T4)</t>
+        </is>
+      </c>
+      <c r="F37" s="26" t="n">
+        <v>28376.42</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Total provisions pour charges versées →</t>
+        </is>
+      </c>
+      <c r="D38" s="11">
+        <f>SUM(D34:D37)</f>
+        <v/>
+      </c>
+      <c r="E38" s="28" t="n"/>
+      <c r="F38" s="11">
+        <f>SUM(F34:F37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="7.55" customHeight="1"/>
+    <row r="40" ht="21.75" customHeight="1">
+      <c r="A40" s="34">
+        <f>IF(F31-F38&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
+        <v/>
+      </c>
+      <c r="D40" s="35">
+        <f>D31-D38</f>
+        <v/>
+      </c>
+      <c r="E40" s="32" t="n"/>
+      <c r="F40" s="35">
+        <f>F31-F38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="27.75" customHeight="1">
+      <c r="A42" s="36" t="inlineStr">
+        <is>
+          <t>ℹ  Clé répartition = surface lot ÷ surface totale site. Période = nombre de jours d'occupation ÷ 365.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A12:B12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.55" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>RÉGULARISATION DE CHARGES — C3 C4 C5</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.8" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Site : ORMES A  |  Année 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.8" customHeight="1">
+      <c r="A3" s="2">
+        <f>Paramètres!$B$8&amp;IF(Paramètres!$E$8&lt;&gt;""," — "&amp;Paramètres!$E$8,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="19.55" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Poste</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Clé répartition</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Total site HT</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>QP annuelle</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Période</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>QP locataire</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>FLUIDES</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15.05" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>Eau</t>
+        </is>
+      </c>
+      <c r="B6" s="25">
+        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C6" s="26">
+        <f>'Récapitulatif 2025'!E10</f>
+        <v/>
+      </c>
+      <c r="D6" s="26">
+        <f>B6*C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="27">
+        <f>Paramètres!$H$8/365</f>
+        <v/>
+      </c>
+      <c r="F6" s="26">
+        <f>D6*E6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15.05" customHeight="1">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>Electricité</t>
+        </is>
+      </c>
+      <c r="B7" s="25">
+        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C7" s="26">
+        <f>'Récapitulatif 2025'!E21</f>
+        <v/>
+      </c>
+      <c r="D7" s="26">
+        <f>B7*C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="27">
+        <f>Paramètres!$H$8/365</f>
+        <v/>
+      </c>
+      <c r="F7" s="26">
+        <f>D7*E7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15.05" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>Gaz</t>
+        </is>
+      </c>
+      <c r="B8" s="25">
+        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C8" s="26">
+        <f>'Récapitulatif 2025'!E32</f>
+        <v/>
+      </c>
+      <c r="D8" s="26">
+        <f>B8*C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="27">
+        <f>Paramètres!$H$8/365</f>
+        <v/>
+      </c>
+      <c r="F8" s="26">
+        <f>D8*E8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Sous-total — FLUIDES</t>
+        </is>
+      </c>
+      <c r="C9" s="11">
+        <f>SUM(C6:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="11">
+        <f>SUM(D6:D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="28" t="n"/>
+      <c r="F9" s="11">
+        <f>SUM(F6:F8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>TRAVAUX</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15.05" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>Entretien Courant</t>
+        </is>
+      </c>
+      <c r="B11" s="25">
+        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C11" s="26">
+        <f>'Récapitulatif 2025'!E37</f>
+        <v/>
+      </c>
+      <c r="D11" s="26">
+        <f>B11*C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="27">
+        <f>Paramètres!$H$8/365</f>
+        <v/>
+      </c>
+      <c r="F11" s="26">
+        <f>D11*E11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Sous-total — TRAVAUX</t>
+        </is>
+      </c>
+      <c r="C12" s="11">
+        <f>SUM(C11:C11)</f>
+        <v/>
+      </c>
+      <c r="D12" s="11">
+        <f>SUM(D11:D11)</f>
+        <v/>
+      </c>
+      <c r="E12" s="28" t="n"/>
+      <c r="F12" s="11">
+        <f>SUM(F11:F11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>CONTRAT MAINTENANCE</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="15.05" customHeight="1">
-      <c r="A14" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Sécurité</t>
-        </is>
-      </c>
-      <c r="B14" s="23">
-        <f>(Paramètres!$C$7/Paramètres!$C$3)</f>
-        <v/>
-      </c>
-      <c r="C14" s="24">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>Espaces Verts</t>
+        </is>
+      </c>
+      <c r="B14" s="25">
+        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C14" s="26">
+        <f>'Récapitulatif 2025'!E46</f>
+        <v/>
+      </c>
+      <c r="D14" s="26">
+        <f>B14*C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="27">
+        <f>Paramètres!$H$8/365</f>
+        <v/>
+      </c>
+      <c r="F14" s="26">
+        <f>D14*E14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15.05" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="B15" s="25">
+        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C15" s="26">
+        <f>'Récapitulatif 2025'!E50</f>
+        <v/>
+      </c>
+      <c r="D15" s="26">
+        <f>B15*C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="27">
+        <f>Paramètres!$H$8/365</f>
+        <v/>
+      </c>
+      <c r="F15" s="26">
+        <f>D15*E15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.05" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>Sécurité</t>
+        </is>
+      </c>
+      <c r="B16" s="25">
+        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C16" s="26">
         <f>'Récapitulatif 2025'!E54</f>
         <v/>
       </c>
-      <c r="D14" s="24">
-        <f>B14*C14</f>
-        <v/>
-      </c>
-      <c r="E14" s="25">
-        <f>MAX(0,MIN(DATE(2025,12,31),IF(Paramètres!$I$7&gt;0,Paramètres!$I$7,DATE(2025,12,31)))-MAX(DATE(2025,1,1),IF(Paramètres!$F$7&gt;0,Paramètres!$F$7,DATE(2025,1,1)))+1)/365</f>
-        <v/>
-      </c>
-      <c r="F14" s="24">
-        <f>D14*E14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15.05" customHeight="1">
-      <c r="A15" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  SSI</t>
-        </is>
-      </c>
-      <c r="B15" s="23">
-        <f>(Paramètres!$C$7/Paramètres!$C$3)</f>
-        <v/>
-      </c>
-      <c r="C15" s="24">
+      <c r="D16" s="26">
+        <f>B16*C16</f>
+        <v/>
+      </c>
+      <c r="E16" s="27">
+        <f>Paramètres!$H$8/365</f>
+        <v/>
+      </c>
+      <c r="F16" s="26">
+        <f>D16*E16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.05" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>SSI</t>
+        </is>
+      </c>
+      <c r="B17" s="25">
+        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C17" s="26">
         <f>'Récapitulatif 2025'!E59</f>
         <v/>
       </c>
-      <c r="D15" s="24">
-        <f>B15*C15</f>
-        <v/>
-      </c>
-      <c r="E15" s="25">
-        <f>MAX(0,MIN(DATE(2025,12,31),IF(Paramètres!$I$7&gt;0,Paramètres!$I$7,DATE(2025,12,31)))-MAX(DATE(2025,1,1),IF(Paramètres!$F$7&gt;0,Paramètres!$F$7,DATE(2025,1,1)))+1)/365</f>
-        <v/>
-      </c>
-      <c r="F15" s="24">
-        <f>D15*E15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15.05" customHeight="1">
-      <c r="A16" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Toitures</t>
-        </is>
-      </c>
-      <c r="B16" s="23">
-        <f>(Paramètres!$C$7/Paramètres!$C$3)</f>
-        <v/>
-      </c>
-      <c r="C16" s="24">
+      <c r="D17" s="26">
+        <f>B17*C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="27">
+        <f>Paramètres!$H$8/365</f>
+        <v/>
+      </c>
+      <c r="F17" s="26">
+        <f>D17*E17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15.05" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>Toitures</t>
+        </is>
+      </c>
+      <c r="B18" s="25">
+        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C18" s="26">
         <f>'Récapitulatif 2025'!E64</f>
         <v/>
       </c>
-      <c r="D16" s="24">
-        <f>B16*C16</f>
-        <v/>
-      </c>
-      <c r="E16" s="25">
-        <f>MAX(0,MIN(DATE(2025,12,31),IF(Paramètres!$I$7&gt;0,Paramètres!$I$7,DATE(2025,12,31)))-MAX(DATE(2025,1,1),IF(Paramètres!$F$7&gt;0,Paramètres!$F$7,DATE(2025,1,1)))+1)/365</f>
-        <v/>
-      </c>
-      <c r="F16" s="24">
-        <f>D16*E16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15.05" customHeight="1">
-      <c r="A17" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  SPK / RIA / PI</t>
-        </is>
-      </c>
-      <c r="B17" s="23">
-        <f>(Paramètres!$C$7/Paramètres!$C$3)</f>
-        <v/>
-      </c>
-      <c r="C17" s="24">
+      <c r="D18" s="26">
+        <f>B18*C18</f>
+        <v/>
+      </c>
+      <c r="E18" s="27">
+        <f>Paramètres!$H$8/365</f>
+        <v/>
+      </c>
+      <c r="F18" s="26">
+        <f>D18*E18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15.05" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>SPK / RIA / PI</t>
+        </is>
+      </c>
+      <c r="B19" s="25">
+        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C19" s="26">
         <f>'Récapitulatif 2025'!E77</f>
         <v/>
       </c>
-      <c r="D17" s="24">
-        <f>B17*C17</f>
-        <v/>
-      </c>
-      <c r="E17" s="25">
-        <f>MAX(0,MIN(DATE(2025,12,31),IF(Paramètres!$I$7&gt;0,Paramètres!$I$7,DATE(2025,12,31)))-MAX(DATE(2025,1,1),IF(Paramètres!$F$7&gt;0,Paramètres!$F$7,DATE(2025,1,1)))+1)/365</f>
-        <v/>
-      </c>
-      <c r="F17" s="24">
-        <f>D17*E17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15.05" customHeight="1">
-      <c r="A18" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Installations électriques</t>
-        </is>
-      </c>
-      <c r="B18" s="23">
-        <f>(Paramètres!$C$7/35730.0)</f>
-        <v/>
-      </c>
-      <c r="C18" s="24">
+      <c r="D19" s="26">
+        <f>B19*C19</f>
+        <v/>
+      </c>
+      <c r="E19" s="27">
+        <f>Paramètres!$H$8/365</f>
+        <v/>
+      </c>
+      <c r="F19" s="26">
+        <f>D19*E19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15.05" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>Installations électriques</t>
+        </is>
+      </c>
+      <c r="B20" s="25">
+        <f>Paramètres!$C$8/35730.0</f>
+        <v/>
+      </c>
+      <c r="C20" s="26">
         <f>'Récapitulatif 2025'!E83</f>
         <v/>
       </c>
-      <c r="D18" s="24">
-        <f>B18*C18</f>
-        <v/>
-      </c>
-      <c r="E18" s="25">
-        <f>MAX(0,MIN(DATE(2025,12,31),IF(Paramètres!$I$7&gt;0,Paramètres!$I$7,DATE(2025,12,31)))-MAX(DATE(2025,1,1),IF(Paramètres!$F$7&gt;0,Paramètres!$F$7,DATE(2025,1,1)))+1)/365</f>
-        <v/>
-      </c>
-      <c r="F18" s="24">
-        <f>D18*E18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15.05" customHeight="1">
-      <c r="A19" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Protection Foudre</t>
-        </is>
-      </c>
-      <c r="B19" s="23">
-        <f>(Paramètres!$C$7/23820.0)</f>
-        <v/>
-      </c>
-      <c r="C19" s="24">
+      <c r="D20" s="26">
+        <f>B20*C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="27">
+        <f>Paramètres!$H$8/365</f>
+        <v/>
+      </c>
+      <c r="F20" s="26">
+        <f>D20*E20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15.05" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>Protection Foudre</t>
+        </is>
+      </c>
+      <c r="B21" s="25">
+        <f>Paramètres!$C$8/23820.0</f>
+        <v/>
+      </c>
+      <c r="C21" s="26">
         <f>'Récapitulatif 2025'!E88</f>
         <v/>
       </c>
-      <c r="D19" s="24">
-        <f>B19*C19</f>
-        <v/>
-      </c>
-      <c r="E19" s="25">
-        <f>MAX(0,MIN(DATE(2025,12,31),IF(Paramètres!$I$7&gt;0,Paramètres!$I$7,DATE(2025,12,31)))-MAX(DATE(2025,1,1),IF(Paramètres!$F$7&gt;0,Paramètres!$F$7,DATE(2025,1,1)))+1)/365</f>
-        <v/>
-      </c>
-      <c r="F19" s="24">
-        <f>D19*E19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15.05" customHeight="1">
-      <c r="A20" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  GTB</t>
-        </is>
-      </c>
-      <c r="B20" s="23">
-        <f>(Paramètres!$C$7/Paramètres!$C$3)</f>
-        <v/>
-      </c>
-      <c r="C20" s="24">
+      <c r="D21" s="26">
+        <f>B21*C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="27">
+        <f>Paramètres!$H$8/365</f>
+        <v/>
+      </c>
+      <c r="F21" s="26">
+        <f>D21*E21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15.05" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>GTB</t>
+        </is>
+      </c>
+      <c r="B22" s="25">
+        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C22" s="26">
         <f>'Récapitulatif 2025'!E97</f>
         <v/>
       </c>
-      <c r="D20" s="24">
-        <f>B20*C20</f>
-        <v/>
-      </c>
-      <c r="E20" s="25">
-        <f>MAX(0,MIN(DATE(2025,12,31),IF(Paramètres!$I$7&gt;0,Paramètres!$I$7,DATE(2025,12,31)))-MAX(DATE(2025,1,1),IF(Paramètres!$F$7&gt;0,Paramètres!$F$7,DATE(2025,1,1)))+1)/365</f>
-        <v/>
-      </c>
-      <c r="F20" s="24">
-        <f>D20*E20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15.05" customHeight="1">
-      <c r="A21" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Détection Gaz</t>
-        </is>
-      </c>
-      <c r="B21" s="23">
-        <f>(Paramètres!$C$7/Paramètres!$C$3)</f>
-        <v/>
-      </c>
-      <c r="C21" s="24">
+      <c r="D22" s="26">
+        <f>B22*C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="27">
+        <f>Paramètres!$H$8/365</f>
+        <v/>
+      </c>
+      <c r="F22" s="26">
+        <f>D22*E22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15.05" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>Détection Gaz</t>
+        </is>
+      </c>
+      <c r="B23" s="25">
+        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C23" s="26">
         <f>'Récapitulatif 2025'!E101</f>
         <v/>
       </c>
-      <c r="D21" s="24">
-        <f>B21*C21</f>
-        <v/>
-      </c>
-      <c r="E21" s="25">
-        <f>MAX(0,MIN(DATE(2025,12,31),IF(Paramètres!$I$7&gt;0,Paramètres!$I$7,DATE(2025,12,31)))-MAX(DATE(2025,1,1),IF(Paramètres!$F$7&gt;0,Paramètres!$F$7,DATE(2025,1,1)))+1)/365</f>
-        <v/>
-      </c>
-      <c r="F21" s="24">
-        <f>D21*E21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15.05" customHeight="1">
-      <c r="A22" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Vérifications règlementaires</t>
-        </is>
-      </c>
-      <c r="B22" s="23">
-        <f>(Paramètres!$C$7/19945.0)</f>
-        <v/>
-      </c>
-      <c r="C22" s="24">
+      <c r="D23" s="26">
+        <f>B23*C23</f>
+        <v/>
+      </c>
+      <c r="E23" s="27">
+        <f>Paramètres!$H$8/365</f>
+        <v/>
+      </c>
+      <c r="F23" s="26">
+        <f>D23*E23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15.05" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>Vérifications règlementaires</t>
+        </is>
+      </c>
+      <c r="B24" s="25">
+        <f>Paramètres!$C$8/19945.0</f>
+        <v/>
+      </c>
+      <c r="C24" s="26">
         <f>'Récapitulatif 2025'!E104</f>
         <v/>
       </c>
-      <c r="D22" s="24">
-        <f>B22*C22</f>
-        <v/>
-      </c>
-      <c r="E22" s="25">
-        <f>MAX(0,MIN(DATE(2025,12,31),IF(Paramètres!$I$7&gt;0,Paramètres!$I$7,DATE(2025,12,31)))-MAX(DATE(2025,1,1),IF(Paramètres!$F$7&gt;0,Paramètres!$F$7,DATE(2025,1,1)))+1)/365</f>
-        <v/>
-      </c>
-      <c r="F22" s="24">
-        <f>D22*E22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15.05" customHeight="1">
-      <c r="A23" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Portails</t>
-        </is>
-      </c>
-      <c r="B23" s="23">
-        <f>(Paramètres!$C$7/Paramètres!$C$3)</f>
-        <v/>
-      </c>
-      <c r="C23" s="24">
+      <c r="D24" s="26">
+        <f>B24*C24</f>
+        <v/>
+      </c>
+      <c r="E24" s="27">
+        <f>Paramètres!$H$8/365</f>
+        <v/>
+      </c>
+      <c r="F24" s="26">
+        <f>D24*E24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15.05" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Portails</t>
+        </is>
+      </c>
+      <c r="B25" s="25">
+        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C25" s="26">
         <f>'Récapitulatif 2025'!E107</f>
         <v/>
       </c>
-      <c r="D23" s="24">
-        <f>B23*C23</f>
-        <v/>
-      </c>
-      <c r="E23" s="25">
-        <f>MAX(0,MIN(DATE(2025,12,31),IF(Paramètres!$I$7&gt;0,Paramètres!$I$7,DATE(2025,12,31)))-MAX(DATE(2025,1,1),IF(Paramètres!$F$7&gt;0,Paramètres!$F$7,DATE(2025,1,1)))+1)/365</f>
-        <v/>
-      </c>
-      <c r="F23" s="24">
-        <f>D23*E23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="D25" s="26">
+        <f>B25*C25</f>
+        <v/>
+      </c>
+      <c r="E25" s="27">
+        <f>Paramètres!$H$8/365</f>
+        <v/>
+      </c>
+      <c r="F25" s="26">
+        <f>D25*E25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Sous-total — CONTRAT MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="C26" s="11">
+        <f>SUM(C14:C25)</f>
+        <v/>
+      </c>
+      <c r="D26" s="11">
+        <f>SUM(D14:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="28" t="n"/>
+      <c r="F26" s="11">
+        <f>SUM(F14:F25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>ASSURANCES + JURIDIQUE</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15.05" customHeight="1">
-      <c r="A25" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Assurances</t>
-        </is>
-      </c>
-      <c r="B25" s="23">
-        <f>(Paramètres!$C$7/Paramètres!$C$3)</f>
-        <v/>
-      </c>
-      <c r="C25" s="24">
+    <row r="28" ht="15.05" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Assurances</t>
+        </is>
+      </c>
+      <c r="B28" s="25">
+        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C28" s="26">
         <f>'Récapitulatif 2025'!E111</f>
         <v/>
       </c>
-      <c r="D25" s="24">
-        <f>B25*C25</f>
-        <v/>
-      </c>
-      <c r="E25" s="25">
-        <f>MAX(0,MIN(DATE(2025,12,31),IF(Paramètres!$I$7&gt;0,Paramètres!$I$7,DATE(2025,12,31)))-MAX(DATE(2025,1,1),IF(Paramètres!$F$7&gt;0,Paramètres!$F$7,DATE(2025,1,1)))+1)/365</f>
-        <v/>
-      </c>
-      <c r="F25" s="24">
-        <f>D25*E25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>Sous-total — FLUIDES</t>
-        </is>
-      </c>
-      <c r="C27" s="19">
-        <f>SUM(C6:C8)</f>
-        <v/>
-      </c>
-      <c r="D27" s="19">
-        <f>SUM(D6:D8)</f>
-        <v/>
-      </c>
-      <c r="F27" s="19">
-        <f>SUM(F6:F8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>Sous-total — TRAVAUX</t>
-        </is>
-      </c>
-      <c r="C28" s="19">
-        <f>SUM(C10:C10)</f>
-        <v/>
-      </c>
-      <c r="D28" s="19">
-        <f>SUM(D10:D10)</f>
-        <v/>
-      </c>
-      <c r="F28" s="19">
-        <f>SUM(F10:F10)</f>
+      <c r="D28" s="26">
+        <f>B28*C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="27">
+        <f>Paramètres!$H$8/365</f>
+        <v/>
+      </c>
+      <c r="F28" s="26">
+        <f>D28*E28</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>Sous-total — CONTRAT MAINTENANCE</t>
-        </is>
-      </c>
-      <c r="C29" s="19">
-        <f>SUM(C12:C23)</f>
-        <v/>
-      </c>
-      <c r="D29" s="19">
-        <f>SUM(D12:D23)</f>
-        <v/>
-      </c>
-      <c r="F29" s="19">
-        <f>SUM(F12:F23)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Sous-total — ASSURANCES + JURIDIQUE</t>
         </is>
       </c>
-      <c r="C30" s="19">
-        <f>SUM(C25:C25)</f>
-        <v/>
-      </c>
-      <c r="D30" s="19">
-        <f>SUM(D25:D25)</f>
-        <v/>
-      </c>
-      <c r="F30" s="19">
-        <f>SUM(F25:F25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="7.55" customHeight="1"/>
-    <row r="32" ht="21.75" customHeight="1">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="C29" s="11">
+        <f>SUM(C28:C28)</f>
+        <v/>
+      </c>
+      <c r="D29" s="11">
+        <f>SUM(D28:D28)</f>
+        <v/>
+      </c>
+      <c r="E29" s="28" t="n"/>
+      <c r="F29" s="11">
+        <f>SUM(F28:F28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="7.55" customHeight="1"/>
+    <row r="31" ht="21.75" customHeight="1">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t>TOTAL CHARGES RÉCUPÉRABLES RÉELLES (€ HT)</t>
         </is>
       </c>
-      <c r="C32" s="27">
-        <f>C27+C28+C29+C30</f>
-        <v/>
-      </c>
-      <c r="D32" s="27">
-        <f>D27+D28+D29+D30</f>
-        <v/>
-      </c>
-      <c r="E32" s="28" t="n"/>
-      <c r="F32" s="27">
-        <f>F27+F28+F29+F30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="7.55" customHeight="1"/>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="C31" s="30">
+        <f>C9+C12+C26+C29</f>
+        <v/>
+      </c>
+      <c r="D31" s="30">
+        <f>D9+D12+D26+D29</f>
+        <v/>
+      </c>
+      <c r="E31" s="31" t="n"/>
+      <c r="F31" s="30">
+        <f>F9+F12+F26+F29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="7.55" customHeight="1"/>
+    <row r="33" ht="19.55" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Provisions pour charges versées</t>
         </is>
       </c>
-      <c r="D34" s="29" t="inlineStr">
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33" t="inlineStr">
         <is>
           <t>Montant annuel (€)</t>
         </is>
       </c>
-      <c r="F34" s="29" t="inlineStr">
+      <c r="E33" s="32" t="n"/>
+      <c r="F33" s="33" t="inlineStr">
         <is>
           <t>Montant locataire (€)</t>
         </is>
       </c>
     </row>
+    <row r="34" ht="15.8" customHeight="1">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1er trimestre (T1)</t>
+        </is>
+      </c>
+    </row>
     <row r="35" ht="15.8" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1er trimestre (T1)</t>
-        </is>
-      </c>
-      <c r="F35" s="24" t="n">
-        <v>2990.6</v>
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2e trimestre (T2)</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="15.8" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2e trimestre (T2)</t>
-        </is>
-      </c>
-      <c r="F36" s="24" t="n">
-        <v>25284.11</v>
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3e trimestre (T3)</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="15.8" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3e trimestre (T3)</t>
-        </is>
-      </c>
-      <c r="F37" s="24" t="n">
-        <v>28376.42</v>
-      </c>
-    </row>
-    <row r="38" ht="15.8" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  4e trimestre (T4)</t>
         </is>
       </c>
-      <c r="F38" s="24" t="n">
-        <v>28376.42</v>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="18" t="inlineStr">
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>Total provisions pour charges versées →</t>
         </is>
       </c>
-      <c r="F39" s="19">
-        <f>SUM(F35:F38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="7.55" customHeight="1"/>
-    <row r="41" ht="21.75" customHeight="1">
-      <c r="A41" s="30">
-        <f>IF(F32-F39&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
-        <v/>
-      </c>
-      <c r="F41" s="31">
-        <f>F32-F39</f>
-        <v/>
+      <c r="D38" s="11">
+        <f>SUM(D34:D37)</f>
+        <v/>
+      </c>
+      <c r="E38" s="28" t="n"/>
+      <c r="F38" s="11">
+        <f>SUM(F34:F37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="7.55" customHeight="1"/>
+    <row r="40" ht="21.75" customHeight="1">
+      <c r="A40" s="34">
+        <f>IF(F31-F38&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
+        <v/>
+      </c>
+      <c r="D40" s="35">
+        <f>D31-D38</f>
+        <v/>
+      </c>
+      <c r="E40" s="32" t="n"/>
+      <c r="F40" s="35">
+        <f>F31-F38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="27.75" customHeight="1">
+      <c r="A42" s="36" t="inlineStr">
+        <is>
+          <t>ℹ  Clé répartition = surface lot ÷ surface totale site. Période = nombre de jours d'occupation ÷ 365.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A36:B36"/>
+  <mergeCells count="16">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A40:C40"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A12:B12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.55" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>ORMES A — COÛT DE LA VACANCE LOCATIVE 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.8" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Estimation de la perte de charges non récupérées sur les lots vacants</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Surface (m²)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>QP annuelle (€ HT)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Période (j/365)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Coût vacance (€ HT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="37">
+        <f>Paramètres!A7</f>
+        <v/>
+      </c>
+      <c r="B5" s="17">
+        <f>Paramètres!B7</f>
+        <v/>
+      </c>
+      <c r="C5" s="38">
+        <f>Paramètres!C7</f>
+        <v/>
+      </c>
+      <c r="D5" s="26">
+        <f>'C1 C2'!D31</f>
+        <v/>
+      </c>
+      <c r="E5" s="27">
+        <f>Paramètres!H7/365</f>
+        <v/>
+      </c>
+      <c r="F5" s="39">
+        <f>IF(Paramètres!B7="Vacant",'C1 C2'!D31,'C1 C2'!D31*(1-Paramètres!H7/365))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="37">
+        <f>Paramètres!A8</f>
+        <v/>
+      </c>
+      <c r="B6" s="17">
+        <f>Paramètres!B8</f>
+        <v/>
+      </c>
+      <c r="C6" s="38">
+        <f>Paramètres!C8</f>
+        <v/>
+      </c>
+      <c r="D6" s="26">
+        <f>'C3 C4 C5'!D31</f>
+        <v/>
+      </c>
+      <c r="E6" s="27">
+        <f>Paramètres!H8/365</f>
+        <v/>
+      </c>
+      <c r="F6" s="39">
+        <f>IF(Paramètres!B8="Vacant",'C3 C4 C5'!D31,'C3 C4 C5'!D31*(1-Paramètres!H8/365))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="6" customHeight="1"/>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Total QP charges (tous lots)</t>
+        </is>
+      </c>
+      <c r="D8" s="11">
+        <f>SUM(D5:D6)</f>
+        <v/>
+      </c>
+      <c r="E8" s="28" t="n"/>
+      <c r="F8" s="28" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Nombre de lots vacants</t>
+        </is>
+      </c>
+      <c r="D9" s="40">
+        <f>COUNTIF(B5:B6,"Vacant")</f>
+        <v/>
+      </c>
+      <c r="E9" s="28" t="n"/>
+      <c r="F9" s="28" t="n"/>
+    </row>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="19.55" customHeight="1">
+      <c r="A11" s="41" t="inlineStr">
+        <is>
+          <t>Charges non récupérables (Frais Bancaires + CAPEX)</t>
+        </is>
+      </c>
+      <c r="F11" s="42">
+        <f>'Récapitulatif 2025'!E118</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="6" customHeight="1"/>
+    <row r="13" ht="25.55" customHeight="1">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>TOTAL COÛT DE LA VACANCE LOCATIVE (€ HT)</t>
+        </is>
+      </c>
+      <c r="F13" s="44">
+        <f>F5+F6+F11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="19.55" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Part vacance sur total charges site</t>
+        </is>
+      </c>
+      <c r="F15" s="45">
+        <f>IF(D8&gt;0,F13/D8,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="6" customHeight="1"/>
+    <row r="17" ht="27.75" customHeight="1">
+      <c r="A17" s="36" t="inlineStr">
+        <is>
+          <t>ℹ  QP annuelle = Total site HT × clé de répartition. Coût vacance = QP annuelle × fraction de l'année non occupée.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A8:C8"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/regularisation_ORMES_A_2025.xlsx
+++ b/regularisation_ORMES_A_2025.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,7 +78,18 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00444444"/>
       <sz val="9"/>
     </font>
     <font>
@@ -91,12 +102,6 @@
       <name val="Calibri"/>
       <color rgb="00222222"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -119,37 +124,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B3A6B"/>
+        <fgColor rgb="FF1B3A6B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0DDEF"/>
+        <fgColor rgb="FFD0DDEF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E5FA3"/>
+        <fgColor rgb="FF2E5FA3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F4F8"/>
+        <fgColor rgb="FFF2F4F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F5E3"/>
+        <fgColor rgb="FFD5F5E3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDECEA"/>
+        <fgColor rgb="FFFDECEA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E64A19"/>
+        <fgColor rgb="FFE64A19"/>
       </patternFill>
     </fill>
   </fills>
@@ -165,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -204,10 +209,19 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -222,19 +236,31 @@
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -247,33 +273,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -285,10 +299,10 @@
     <xf numFmtId="164" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -659,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3248,8 +3262,33 @@
         <v/>
       </c>
     </row>
+    <row r="119" ht="6" customHeight="1"/>
+    <row r="120" ht="19.55" customHeight="1">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL — CHARGES NON RÉCUPÉRABLES</t>
+        </is>
+      </c>
+      <c r="E120" s="14">
+        <f>E118</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121" ht="6" customHeight="1"/>
+    <row r="122" ht="25.55" customHeight="1">
+      <c r="A122" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL GÉNÉRAL — CHARGES RÉCUPÉRABLES</t>
+        </is>
+      </c>
+      <c r="E122" s="16">
+        <f>E10+E21+E32+E37+E46+E50+E54+E59+E64+E77+E83+E88+E97+E101+E104+E107+E111</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="27">
+    <mergeCell ref="A122:D122"/>
     <mergeCell ref="A97:D97"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A38:G38"/>
@@ -3268,6 +3307,7 @@
     <mergeCell ref="A46:D46"/>
     <mergeCell ref="A118:D118"/>
     <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A120:D120"/>
     <mergeCell ref="A50:D50"/>
     <mergeCell ref="A101:D101"/>
     <mergeCell ref="A21:D21"/>
@@ -3286,7 +3326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3313,7 +3353,7 @@
           <t>Site</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>ORMES A</t>
         </is>
@@ -3325,7 +3365,7 @@
           <t>Surface totale site (m²)</t>
         </is>
       </c>
-      <c r="C3" s="14" t="n">
+      <c r="C3" s="17" t="n">
         <v>29565.91</v>
       </c>
     </row>
@@ -3335,7 +3375,7 @@
           <t>Année</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="17" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -3368,7 +3408,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Début de bail / MAD</t>
+          <t>Début de bail</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -3388,70 +3428,264 @@
       </c>
     </row>
     <row r="7" ht="15.05" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>C1 C2</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Occupé</t>
         </is>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="19" t="n">
         <v>9623</v>
       </c>
-      <c r="D7" s="17" t="inlineStr"/>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>ID LOGISTICS</t>
         </is>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="22" t="n">
         <v>45737</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="22" t="n">
         <v>50119</v>
       </c>
-      <c r="H7" s="20">
-        <f>MAX(0,MIN(DATE(2025,12,31),IF(G7&gt;0,G7,DATE(2025,12,31)))-MAX(DATE(2025,1,1),IF(F7&gt;0,F7,DATE(2025,1,1)))+1)</f>
-        <v/>
-      </c>
-      <c r="I7" s="21">
+      <c r="H7" s="23">
+        <f>MAX(0,MIN(DATE(2025,12,31),IF(G7="",DATE(2025,12,31),G7))-MAX(DATE(2025,1,1),IF(F7="",DATE(2025,1,1),F7))+1)</f>
+        <v/>
+      </c>
+      <c r="I7" s="24">
         <f>H7/365</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15.05" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>C3 C4 C5</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Vacant</t>
         </is>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="19" t="n">
         <v>19942.91</v>
       </c>
-      <c r="D8" s="17" t="inlineStr"/>
-      <c r="E8" s="18" t="inlineStr"/>
-      <c r="F8" s="17" t="n"/>
-      <c r="G8" s="17" t="n"/>
-      <c r="H8" s="20">
-        <f>MAX(0,MIN(DATE(2025,12,31),IF(G8&gt;0,G8,DATE(2025,12,31)))-MAX(DATE(2025,1,1),IF(F8&gt;0,F8,DATE(2025,1,1)))+1)</f>
-        <v/>
-      </c>
-      <c r="I8" s="21">
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="21" t="inlineStr"/>
+      <c r="F8" s="20" t="n"/>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="23">
+        <f>MAX(0,MIN(DATE(2025,12,31),IF(G8="",DATE(2025,12,31),G8))-MAX(DATE(2025,1,1),IF(F8="",DATE(2025,1,1),F8))+1)</f>
+        <v/>
+      </c>
+      <c r="I8" s="24">
         <f>H8/365</f>
         <v/>
       </c>
     </row>
+    <row r="9" ht="7.55" customHeight="1"/>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>Poste (lié au Récapitulatif)</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>Montant HT (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15.05" customHeight="1">
+      <c r="A11" s="28">
+        <f>IFERROR(MID('Récapitulatif 2025'!A10,FIND(" — ",'Récapitulatif 2025'!A10)+4,100),"")</f>
+        <v/>
+      </c>
+      <c r="C11" s="29">
+        <f>'Récapitulatif 2025'!E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15.05" customHeight="1">
+      <c r="A12" s="28">
+        <f>IFERROR(MID('Récapitulatif 2025'!A21,FIND(" — ",'Récapitulatif 2025'!A21)+4,100),"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="29">
+        <f>'Récapitulatif 2025'!E21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15.05" customHeight="1">
+      <c r="A13" s="28">
+        <f>IFERROR(MID('Récapitulatif 2025'!A32,FIND(" — ",'Récapitulatif 2025'!A32)+4,100),"")</f>
+        <v/>
+      </c>
+      <c r="C13" s="29">
+        <f>'Récapitulatif 2025'!E32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.05" customHeight="1">
+      <c r="A14" s="28">
+        <f>IFERROR(MID('Récapitulatif 2025'!A37,FIND(" — ",'Récapitulatif 2025'!A37)+4,100),"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="29">
+        <f>'Récapitulatif 2025'!E37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15.05" customHeight="1">
+      <c r="A15" s="28">
+        <f>IFERROR(MID('Récapitulatif 2025'!A46,FIND(" — ",'Récapitulatif 2025'!A46)+4,100),"")</f>
+        <v/>
+      </c>
+      <c r="C15" s="29">
+        <f>'Récapitulatif 2025'!E46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.05" customHeight="1">
+      <c r="A16" s="28">
+        <f>IFERROR(MID('Récapitulatif 2025'!A50,FIND(" — ",'Récapitulatif 2025'!A50)+4,100),"")</f>
+        <v/>
+      </c>
+      <c r="C16" s="29">
+        <f>'Récapitulatif 2025'!E50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.05" customHeight="1">
+      <c r="A17" s="28">
+        <f>IFERROR(MID('Récapitulatif 2025'!A54,FIND(" — ",'Récapitulatif 2025'!A54)+4,100),"")</f>
+        <v/>
+      </c>
+      <c r="C17" s="29">
+        <f>'Récapitulatif 2025'!E54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15.05" customHeight="1">
+      <c r="A18" s="28">
+        <f>IFERROR(MID('Récapitulatif 2025'!A59,FIND(" — ",'Récapitulatif 2025'!A59)+4,100),"")</f>
+        <v/>
+      </c>
+      <c r="C18" s="29">
+        <f>'Récapitulatif 2025'!E59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15.05" customHeight="1">
+      <c r="A19" s="28">
+        <f>IFERROR(MID('Récapitulatif 2025'!A64,FIND(" — ",'Récapitulatif 2025'!A64)+4,100),"")</f>
+        <v/>
+      </c>
+      <c r="C19" s="29">
+        <f>'Récapitulatif 2025'!E64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15.05" customHeight="1">
+      <c r="A20" s="28">
+        <f>IFERROR(MID('Récapitulatif 2025'!A77,FIND(" — ",'Récapitulatif 2025'!A77)+4,100),"")</f>
+        <v/>
+      </c>
+      <c r="C20" s="29">
+        <f>'Récapitulatif 2025'!E77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15.05" customHeight="1">
+      <c r="A21" s="28">
+        <f>IFERROR(MID('Récapitulatif 2025'!A83,FIND(" — ",'Récapitulatif 2025'!A83)+4,100),"")</f>
+        <v/>
+      </c>
+      <c r="C21" s="29">
+        <f>'Récapitulatif 2025'!E83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15.05" customHeight="1">
+      <c r="A22" s="28">
+        <f>IFERROR(MID('Récapitulatif 2025'!A88,FIND(" — ",'Récapitulatif 2025'!A88)+4,100),"")</f>
+        <v/>
+      </c>
+      <c r="C22" s="29">
+        <f>'Récapitulatif 2025'!E88</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15.05" customHeight="1">
+      <c r="A23" s="28">
+        <f>IFERROR(MID('Récapitulatif 2025'!A97,FIND(" — ",'Récapitulatif 2025'!A97)+4,100),"")</f>
+        <v/>
+      </c>
+      <c r="C23" s="29">
+        <f>'Récapitulatif 2025'!E97</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15.05" customHeight="1">
+      <c r="A24" s="28">
+        <f>IFERROR(MID('Récapitulatif 2025'!A101,FIND(" — ",'Récapitulatif 2025'!A101)+4,100),"")</f>
+        <v/>
+      </c>
+      <c r="C24" s="29">
+        <f>'Récapitulatif 2025'!E101</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15.05" customHeight="1">
+      <c r="A25" s="28">
+        <f>IFERROR(MID('Récapitulatif 2025'!A104,FIND(" — ",'Récapitulatif 2025'!A104)+4,100),"")</f>
+        <v/>
+      </c>
+      <c r="C25" s="29">
+        <f>'Récapitulatif 2025'!E104</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15.05" customHeight="1">
+      <c r="A26" s="28">
+        <f>IFERROR(MID('Récapitulatif 2025'!A107,FIND(" — ",'Récapitulatif 2025'!A107)+4,100),"")</f>
+        <v/>
+      </c>
+      <c r="C26" s="29">
+        <f>'Récapitulatif 2025'!E107</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15.05" customHeight="1">
+      <c r="A27" s="28">
+        <f>IFERROR(MID('Récapitulatif 2025'!A111,FIND(" — ",'Récapitulatif 2025'!A111)+4,100),"")</f>
+        <v/>
+      </c>
+      <c r="C27" s="29">
+        <f>'Récapitulatif 2025'!E111</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15.05" customHeight="1">
+      <c r="A28" s="28">
+        <f>IFERROR(MID('Récapitulatif 2025'!A118,FIND(" — ",'Récapitulatif 2025'!A118)+4,100),"")</f>
+        <v/>
+      </c>
+      <c r="C28" s="29">
+        <f>'Récapitulatif 2025'!E118</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3474,7 +3708,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.55" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>RÉGULARISATION DE CHARGES — C1 C2</t>
         </is>
@@ -3533,82 +3767,82 @@
       </c>
     </row>
     <row r="6" ht="15.05" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>Eau</t>
         </is>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="32">
         <f>Paramètres!$C$7/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="33">
         <f>'Récapitulatif 2025'!E10</f>
         <v/>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="33">
         <f>B6*C6</f>
         <v/>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="34">
         <f>Paramètres!$H$7/365</f>
         <v/>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="33">
         <f>D6*E6</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15.05" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>Electricité</t>
         </is>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="32">
         <f>Paramètres!$C$7/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="33">
         <f>'Récapitulatif 2025'!E21</f>
         <v/>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="33">
         <f>B7*C7</f>
         <v/>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="34">
         <f>Paramètres!$H$7/365</f>
         <v/>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="33">
         <f>D7*E7</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15.05" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>Gaz</t>
         </is>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="32">
         <f>Paramètres!$C$7/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="33">
         <f>'Récapitulatif 2025'!E32</f>
         <v/>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="33">
         <f>B8*C8</f>
         <v/>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="34">
         <f>Paramètres!$H$7/365</f>
         <v/>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="33">
         <f>D8*E8</f>
         <v/>
       </c>
@@ -3627,7 +3861,7 @@
         <f>SUM(D6:D8)</f>
         <v/>
       </c>
-      <c r="E9" s="28" t="n"/>
+      <c r="E9" s="35" t="n"/>
       <c r="F9" s="11">
         <f>SUM(F6:F8)</f>
         <v/>
@@ -3641,28 +3875,28 @@
       </c>
     </row>
     <row r="11" ht="15.05" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>Entretien Courant</t>
         </is>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="32">
         <f>Paramètres!$C$7/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="33">
         <f>'Récapitulatif 2025'!E37</f>
         <v/>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="33">
         <f>B11*C11</f>
         <v/>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="34">
         <f>Paramètres!$H$7/365</f>
         <v/>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="33">
         <f>D11*E11</f>
         <v/>
       </c>
@@ -3681,7 +3915,7 @@
         <f>SUM(D11:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="28" t="n"/>
+      <c r="E12" s="35" t="n"/>
       <c r="F12" s="11">
         <f>SUM(F11:F11)</f>
         <v/>
@@ -3695,325 +3929,325 @@
       </c>
     </row>
     <row r="14" ht="15.05" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>Espaces Verts</t>
         </is>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="32">
         <f>Paramètres!$C$7/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="33">
         <f>'Récapitulatif 2025'!E46</f>
         <v/>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="33">
         <f>B14*C14</f>
         <v/>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="34">
         <f>Paramètres!$H$7/365</f>
         <v/>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="33">
         <f>D14*E14</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15.05" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>CVC</t>
         </is>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="32">
         <f>Paramètres!$C$7/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="33">
         <f>'Récapitulatif 2025'!E50</f>
         <v/>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="33">
         <f>B15*C15</f>
         <v/>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="34">
         <f>Paramètres!$H$7/365</f>
         <v/>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="33">
         <f>D15*E15</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15.05" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>Sécurité</t>
         </is>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="32">
         <f>Paramètres!$C$7/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="33">
         <f>'Récapitulatif 2025'!E54</f>
         <v/>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="33">
         <f>B16*C16</f>
         <v/>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="34">
         <f>Paramètres!$H$7/365</f>
         <v/>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="33">
         <f>D16*E16</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15.05" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>SSI</t>
         </is>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="32">
         <f>Paramètres!$C$7/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="33">
         <f>'Récapitulatif 2025'!E59</f>
         <v/>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="33">
         <f>B17*C17</f>
         <v/>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="34">
         <f>Paramètres!$H$7/365</f>
         <v/>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="33">
         <f>D17*E17</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15.05" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>Toitures</t>
         </is>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="32">
         <f>Paramètres!$C$7/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="33">
         <f>'Récapitulatif 2025'!E64</f>
         <v/>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="33">
         <f>B18*C18</f>
         <v/>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="34">
         <f>Paramètres!$H$7/365</f>
         <v/>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="33">
         <f>D18*E18</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15.05" customHeight="1">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>SPK / RIA / PI</t>
         </is>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="32">
         <f>Paramètres!$C$7/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="33">
         <f>'Récapitulatif 2025'!E77</f>
         <v/>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="33">
         <f>B19*C19</f>
         <v/>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="34">
         <f>Paramètres!$H$7/365</f>
         <v/>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="33">
         <f>D19*E19</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15.05" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>Installations électriques</t>
         </is>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="32">
         <f>Paramètres!$C$7/35730.0</f>
         <v/>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="33">
         <f>'Récapitulatif 2025'!E83</f>
         <v/>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="33">
         <f>B20*C20</f>
         <v/>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="34">
         <f>Paramètres!$H$7/365</f>
         <v/>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="33">
         <f>D20*E20</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15.05" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>Protection Foudre</t>
         </is>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="32">
         <f>Paramètres!$C$7/23820.0</f>
         <v/>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="33">
         <f>'Récapitulatif 2025'!E88</f>
         <v/>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="33">
         <f>B21*C21</f>
         <v/>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="34">
         <f>Paramètres!$H$7/365</f>
         <v/>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="33">
         <f>D21*E21</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15.05" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t>GTB</t>
         </is>
       </c>
-      <c r="B22" s="25">
+      <c r="B22" s="32">
         <f>Paramètres!$C$7/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="33">
         <f>'Récapitulatif 2025'!E97</f>
         <v/>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="33">
         <f>B22*C22</f>
         <v/>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="34">
         <f>Paramètres!$H$7/365</f>
         <v/>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="33">
         <f>D22*E22</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15.05" customHeight="1">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>Détection Gaz</t>
         </is>
       </c>
-      <c r="B23" s="25">
+      <c r="B23" s="32">
         <f>Paramètres!$C$7/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="33">
         <f>'Récapitulatif 2025'!E101</f>
         <v/>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="33">
         <f>B23*C23</f>
         <v/>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="34">
         <f>Paramètres!$H$7/365</f>
         <v/>
       </c>
-      <c r="F23" s="26">
+      <c r="F23" s="33">
         <f>D23*E23</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15.05" customHeight="1">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>Vérifications règlementaires</t>
         </is>
       </c>
-      <c r="B24" s="25">
+      <c r="B24" s="32">
         <f>Paramètres!$C$7/19945.0</f>
         <v/>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="33">
         <f>'Récapitulatif 2025'!E104</f>
         <v/>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="33">
         <f>B24*C24</f>
         <v/>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="34">
         <f>Paramètres!$H$7/365</f>
         <v/>
       </c>
-      <c r="F24" s="26">
+      <c r="F24" s="33">
         <f>D24*E24</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15.05" customHeight="1">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>Portails</t>
         </is>
       </c>
-      <c r="B25" s="25">
+      <c r="B25" s="32">
         <f>Paramètres!$C$7/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="33">
         <f>'Récapitulatif 2025'!E107</f>
         <v/>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="33">
         <f>B25*C25</f>
         <v/>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="34">
         <f>Paramètres!$H$7/365</f>
         <v/>
       </c>
-      <c r="F25" s="26">
+      <c r="F25" s="33">
         <f>D25*E25</f>
         <v/>
       </c>
@@ -4032,7 +4266,7 @@
         <f>SUM(D14:D25)</f>
         <v/>
       </c>
-      <c r="E26" s="28" t="n"/>
+      <c r="E26" s="35" t="n"/>
       <c r="F26" s="11">
         <f>SUM(F14:F25)</f>
         <v/>
@@ -4046,28 +4280,28 @@
       </c>
     </row>
     <row r="28" ht="15.05" customHeight="1">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="31" t="inlineStr">
         <is>
           <t>Assurances</t>
         </is>
       </c>
-      <c r="B28" s="25">
+      <c r="B28" s="32">
         <f>Paramètres!$C$7/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C28" s="26">
+      <c r="C28" s="33">
         <f>'Récapitulatif 2025'!E111</f>
         <v/>
       </c>
-      <c r="D28" s="26">
+      <c r="D28" s="33">
         <f>B28*C28</f>
         <v/>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="34">
         <f>Paramètres!$H$7/365</f>
         <v/>
       </c>
-      <c r="F28" s="26">
+      <c r="F28" s="33">
         <f>D28*E28</f>
         <v/>
       </c>
@@ -4086,7 +4320,7 @@
         <f>SUM(D28:D28)</f>
         <v/>
       </c>
-      <c r="E29" s="28" t="n"/>
+      <c r="E29" s="35" t="n"/>
       <c r="F29" s="11">
         <f>SUM(F28:F28)</f>
         <v/>
@@ -4094,21 +4328,21 @@
     </row>
     <row r="30" ht="7.55" customHeight="1"/>
     <row r="31" ht="21.75" customHeight="1">
-      <c r="A31" s="29" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>TOTAL CHARGES RÉCUPÉRABLES RÉELLES (€ HT)</t>
         </is>
       </c>
-      <c r="C31" s="30">
+      <c r="C31" s="16">
         <f>C9+C12+C26+C29</f>
         <v/>
       </c>
-      <c r="D31" s="30">
+      <c r="D31" s="16">
         <f>D9+D12+D26+D29</f>
         <v/>
       </c>
-      <c r="E31" s="31" t="n"/>
-      <c r="F31" s="30">
+      <c r="E31" s="36" t="n"/>
+      <c r="F31" s="16">
         <f>F9+F12+F26+F29</f>
         <v/>
       </c>
@@ -4120,56 +4354,56 @@
           <t>Provisions pour charges versées</t>
         </is>
       </c>
-      <c r="C33" s="32" t="n"/>
-      <c r="D33" s="33" t="inlineStr">
+      <c r="C33" s="37" t="n"/>
+      <c r="D33" s="27" t="inlineStr">
         <is>
           <t>Montant annuel (€)</t>
         </is>
       </c>
-      <c r="E33" s="32" t="n"/>
-      <c r="F33" s="33" t="inlineStr">
+      <c r="E33" s="37" t="n"/>
+      <c r="F33" s="27" t="inlineStr">
         <is>
           <t>Montant locataire (€)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.8" customHeight="1">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  1er trimestre (T1)</t>
         </is>
       </c>
-      <c r="F34" s="26" t="n">
+      <c r="F34" s="33" t="n">
         <v>2990.6</v>
       </c>
     </row>
     <row r="35" ht="15.8" customHeight="1">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  2e trimestre (T2)</t>
         </is>
       </c>
-      <c r="F35" s="26" t="n">
+      <c r="F35" s="33" t="n">
         <v>25284.11</v>
       </c>
     </row>
     <row r="36" ht="15.8" customHeight="1">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  3e trimestre (T3)</t>
         </is>
       </c>
-      <c r="F36" s="26" t="n">
+      <c r="F36" s="33" t="n">
         <v>28376.42</v>
       </c>
     </row>
     <row r="37" ht="15.8" customHeight="1">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  4e trimestre (T4)</t>
         </is>
       </c>
-      <c r="F37" s="26" t="n">
+      <c r="F37" s="33" t="n">
         <v>28376.42</v>
       </c>
     </row>
@@ -4183,7 +4417,7 @@
         <f>SUM(D34:D37)</f>
         <v/>
       </c>
-      <c r="E38" s="28" t="n"/>
+      <c r="E38" s="35" t="n"/>
       <c r="F38" s="11">
         <f>SUM(F34:F37)</f>
         <v/>
@@ -4191,22 +4425,22 @@
     </row>
     <row r="39" ht="7.55" customHeight="1"/>
     <row r="40" ht="21.75" customHeight="1">
-      <c r="A40" s="34">
+      <c r="A40" s="38">
         <f>IF(F31-F38&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
         <v/>
       </c>
-      <c r="D40" s="35">
+      <c r="D40" s="39">
         <f>D31-D38</f>
         <v/>
       </c>
-      <c r="E40" s="32" t="n"/>
-      <c r="F40" s="35">
+      <c r="E40" s="37" t="n"/>
+      <c r="F40" s="39">
         <f>F31-F38</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="27.75" customHeight="1">
-      <c r="A42" s="36" t="inlineStr">
+      <c r="A42" s="40" t="inlineStr">
         <is>
           <t>ℹ  Clé répartition = surface lot ÷ surface totale site. Période = nombre de jours d'occupation ÷ 365.</t>
         </is>
@@ -4252,7 +4486,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.55" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>RÉGULARISATION DE CHARGES — C3 C4 C5</t>
         </is>
@@ -4311,82 +4545,82 @@
       </c>
     </row>
     <row r="6" ht="15.05" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>Eau</t>
         </is>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="32">
         <f>Paramètres!$C$8/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="33">
         <f>'Récapitulatif 2025'!E10</f>
         <v/>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="33">
         <f>B6*C6</f>
         <v/>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="34">
         <f>Paramètres!$H$8/365</f>
         <v/>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="33">
         <f>D6*E6</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15.05" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>Electricité</t>
         </is>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="32">
         <f>Paramètres!$C$8/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="33">
         <f>'Récapitulatif 2025'!E21</f>
         <v/>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="33">
         <f>B7*C7</f>
         <v/>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="34">
         <f>Paramètres!$H$8/365</f>
         <v/>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="33">
         <f>D7*E7</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15.05" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>Gaz</t>
         </is>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="32">
         <f>Paramètres!$C$8/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="33">
         <f>'Récapitulatif 2025'!E32</f>
         <v/>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="33">
         <f>B8*C8</f>
         <v/>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="34">
         <f>Paramètres!$H$8/365</f>
         <v/>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="33">
         <f>D8*E8</f>
         <v/>
       </c>
@@ -4405,7 +4639,7 @@
         <f>SUM(D6:D8)</f>
         <v/>
       </c>
-      <c r="E9" s="28" t="n"/>
+      <c r="E9" s="35" t="n"/>
       <c r="F9" s="11">
         <f>SUM(F6:F8)</f>
         <v/>
@@ -4419,28 +4653,28 @@
       </c>
     </row>
     <row r="11" ht="15.05" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>Entretien Courant</t>
         </is>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="32">
         <f>Paramètres!$C$8/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="33">
         <f>'Récapitulatif 2025'!E37</f>
         <v/>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="33">
         <f>B11*C11</f>
         <v/>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="34">
         <f>Paramètres!$H$8/365</f>
         <v/>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="33">
         <f>D11*E11</f>
         <v/>
       </c>
@@ -4459,7 +4693,7 @@
         <f>SUM(D11:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="28" t="n"/>
+      <c r="E12" s="35" t="n"/>
       <c r="F12" s="11">
         <f>SUM(F11:F11)</f>
         <v/>
@@ -4473,325 +4707,325 @@
       </c>
     </row>
     <row r="14" ht="15.05" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>Espaces Verts</t>
         </is>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="32">
         <f>Paramètres!$C$8/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="33">
         <f>'Récapitulatif 2025'!E46</f>
         <v/>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="33">
         <f>B14*C14</f>
         <v/>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="34">
         <f>Paramètres!$H$8/365</f>
         <v/>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="33">
         <f>D14*E14</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15.05" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>CVC</t>
         </is>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="32">
         <f>Paramètres!$C$8/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="33">
         <f>'Récapitulatif 2025'!E50</f>
         <v/>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="33">
         <f>B15*C15</f>
         <v/>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="34">
         <f>Paramètres!$H$8/365</f>
         <v/>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="33">
         <f>D15*E15</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15.05" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>Sécurité</t>
         </is>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="32">
         <f>Paramètres!$C$8/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="33">
         <f>'Récapitulatif 2025'!E54</f>
         <v/>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="33">
         <f>B16*C16</f>
         <v/>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="34">
         <f>Paramètres!$H$8/365</f>
         <v/>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="33">
         <f>D16*E16</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15.05" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>SSI</t>
         </is>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="32">
         <f>Paramètres!$C$8/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="33">
         <f>'Récapitulatif 2025'!E59</f>
         <v/>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="33">
         <f>B17*C17</f>
         <v/>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="34">
         <f>Paramètres!$H$8/365</f>
         <v/>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="33">
         <f>D17*E17</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15.05" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>Toitures</t>
         </is>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="32">
         <f>Paramètres!$C$8/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="33">
         <f>'Récapitulatif 2025'!E64</f>
         <v/>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="33">
         <f>B18*C18</f>
         <v/>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="34">
         <f>Paramètres!$H$8/365</f>
         <v/>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="33">
         <f>D18*E18</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15.05" customHeight="1">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>SPK / RIA / PI</t>
         </is>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="32">
         <f>Paramètres!$C$8/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="33">
         <f>'Récapitulatif 2025'!E77</f>
         <v/>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="33">
         <f>B19*C19</f>
         <v/>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="34">
         <f>Paramètres!$H$8/365</f>
         <v/>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="33">
         <f>D19*E19</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15.05" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>Installations électriques</t>
         </is>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="32">
         <f>Paramètres!$C$8/35730.0</f>
         <v/>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="33">
         <f>'Récapitulatif 2025'!E83</f>
         <v/>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="33">
         <f>B20*C20</f>
         <v/>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="34">
         <f>Paramètres!$H$8/365</f>
         <v/>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="33">
         <f>D20*E20</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15.05" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>Protection Foudre</t>
         </is>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="32">
         <f>Paramètres!$C$8/23820.0</f>
         <v/>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="33">
         <f>'Récapitulatif 2025'!E88</f>
         <v/>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="33">
         <f>B21*C21</f>
         <v/>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="34">
         <f>Paramètres!$H$8/365</f>
         <v/>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="33">
         <f>D21*E21</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15.05" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t>GTB</t>
         </is>
       </c>
-      <c r="B22" s="25">
+      <c r="B22" s="32">
         <f>Paramètres!$C$8/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="33">
         <f>'Récapitulatif 2025'!E97</f>
         <v/>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="33">
         <f>B22*C22</f>
         <v/>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="34">
         <f>Paramètres!$H$8/365</f>
         <v/>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="33">
         <f>D22*E22</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15.05" customHeight="1">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>Détection Gaz</t>
         </is>
       </c>
-      <c r="B23" s="25">
+      <c r="B23" s="32">
         <f>Paramètres!$C$8/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="33">
         <f>'Récapitulatif 2025'!E101</f>
         <v/>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="33">
         <f>B23*C23</f>
         <v/>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="34">
         <f>Paramètres!$H$8/365</f>
         <v/>
       </c>
-      <c r="F23" s="26">
+      <c r="F23" s="33">
         <f>D23*E23</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15.05" customHeight="1">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>Vérifications règlementaires</t>
         </is>
       </c>
-      <c r="B24" s="25">
+      <c r="B24" s="32">
         <f>Paramètres!$C$8/19945.0</f>
         <v/>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="33">
         <f>'Récapitulatif 2025'!E104</f>
         <v/>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="33">
         <f>B24*C24</f>
         <v/>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="34">
         <f>Paramètres!$H$8/365</f>
         <v/>
       </c>
-      <c r="F24" s="26">
+      <c r="F24" s="33">
         <f>D24*E24</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15.05" customHeight="1">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>Portails</t>
         </is>
       </c>
-      <c r="B25" s="25">
+      <c r="B25" s="32">
         <f>Paramètres!$C$8/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="33">
         <f>'Récapitulatif 2025'!E107</f>
         <v/>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="33">
         <f>B25*C25</f>
         <v/>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="34">
         <f>Paramètres!$H$8/365</f>
         <v/>
       </c>
-      <c r="F25" s="26">
+      <c r="F25" s="33">
         <f>D25*E25</f>
         <v/>
       </c>
@@ -4810,7 +5044,7 @@
         <f>SUM(D14:D25)</f>
         <v/>
       </c>
-      <c r="E26" s="28" t="n"/>
+      <c r="E26" s="35" t="n"/>
       <c r="F26" s="11">
         <f>SUM(F14:F25)</f>
         <v/>
@@ -4824,28 +5058,28 @@
       </c>
     </row>
     <row r="28" ht="15.05" customHeight="1">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="31" t="inlineStr">
         <is>
           <t>Assurances</t>
         </is>
       </c>
-      <c r="B28" s="25">
+      <c r="B28" s="32">
         <f>Paramètres!$C$8/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C28" s="26">
+      <c r="C28" s="33">
         <f>'Récapitulatif 2025'!E111</f>
         <v/>
       </c>
-      <c r="D28" s="26">
+      <c r="D28" s="33">
         <f>B28*C28</f>
         <v/>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="34">
         <f>Paramètres!$H$8/365</f>
         <v/>
       </c>
-      <c r="F28" s="26">
+      <c r="F28" s="33">
         <f>D28*E28</f>
         <v/>
       </c>
@@ -4864,7 +5098,7 @@
         <f>SUM(D28:D28)</f>
         <v/>
       </c>
-      <c r="E29" s="28" t="n"/>
+      <c r="E29" s="35" t="n"/>
       <c r="F29" s="11">
         <f>SUM(F28:F28)</f>
         <v/>
@@ -4872,21 +5106,21 @@
     </row>
     <row r="30" ht="7.55" customHeight="1"/>
     <row r="31" ht="21.75" customHeight="1">
-      <c r="A31" s="29" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>TOTAL CHARGES RÉCUPÉRABLES RÉELLES (€ HT)</t>
         </is>
       </c>
-      <c r="C31" s="30">
+      <c r="C31" s="16">
         <f>C9+C12+C26+C29</f>
         <v/>
       </c>
-      <c r="D31" s="30">
+      <c r="D31" s="16">
         <f>D9+D12+D26+D29</f>
         <v/>
       </c>
-      <c r="E31" s="31" t="n"/>
-      <c r="F31" s="30">
+      <c r="E31" s="36" t="n"/>
+      <c r="F31" s="16">
         <f>F9+F12+F26+F29</f>
         <v/>
       </c>
@@ -4898,42 +5132,42 @@
           <t>Provisions pour charges versées</t>
         </is>
       </c>
-      <c r="C33" s="32" t="n"/>
-      <c r="D33" s="33" t="inlineStr">
+      <c r="C33" s="37" t="n"/>
+      <c r="D33" s="27" t="inlineStr">
         <is>
           <t>Montant annuel (€)</t>
         </is>
       </c>
-      <c r="E33" s="32" t="n"/>
-      <c r="F33" s="33" t="inlineStr">
+      <c r="E33" s="37" t="n"/>
+      <c r="F33" s="27" t="inlineStr">
         <is>
           <t>Montant locataire (€)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.8" customHeight="1">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  1er trimestre (T1)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.8" customHeight="1">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  2e trimestre (T2)</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.8" customHeight="1">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  3e trimestre (T3)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.8" customHeight="1">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  4e trimestre (T4)</t>
         </is>
@@ -4949,7 +5183,7 @@
         <f>SUM(D34:D37)</f>
         <v/>
       </c>
-      <c r="E38" s="28" t="n"/>
+      <c r="E38" s="35" t="n"/>
       <c r="F38" s="11">
         <f>SUM(F34:F37)</f>
         <v/>
@@ -4957,22 +5191,22 @@
     </row>
     <row r="39" ht="7.55" customHeight="1"/>
     <row r="40" ht="21.75" customHeight="1">
-      <c r="A40" s="34">
+      <c r="A40" s="38">
         <f>IF(F31-F38&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
         <v/>
       </c>
-      <c r="D40" s="35">
+      <c r="D40" s="39">
         <f>D31-D38</f>
         <v/>
       </c>
-      <c r="E40" s="32" t="n"/>
-      <c r="F40" s="35">
+      <c r="E40" s="37" t="n"/>
+      <c r="F40" s="39">
         <f>F31-F38</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="27.75" customHeight="1">
-      <c r="A42" s="36" t="inlineStr">
+      <c r="A42" s="40" t="inlineStr">
         <is>
           <t>ℹ  Clé répartition = surface lot ÷ surface totale site. Période = nombre de jours d'occupation ÷ 365.</t>
         </is>
@@ -5019,7 +5253,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.55" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>ORMES A — COÛT DE LA VACANCE LOCATIVE 2025</t>
         </is>
@@ -5066,54 +5300,54 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="37">
+      <c r="A5" s="41">
         <f>Paramètres!A7</f>
         <v/>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="20">
         <f>Paramètres!B7</f>
         <v/>
       </c>
-      <c r="C5" s="38">
+      <c r="C5" s="42">
         <f>Paramètres!C7</f>
         <v/>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="33">
         <f>'C1 C2'!D31</f>
         <v/>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="34">
         <f>Paramètres!H7/365</f>
         <v/>
       </c>
-      <c r="F5" s="39">
-        <f>IF(Paramètres!B7="Vacant",'C1 C2'!D31,'C1 C2'!D31*(1-Paramètres!H7/365))</f>
+      <c r="F5" s="29">
+        <f>IF(Paramètres!B7="Vacant",'C1 C2'!D31,'C1 C2'!D31-'C1 C2'!F31)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="37">
+      <c r="A6" s="41">
         <f>Paramètres!A8</f>
         <v/>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="20">
         <f>Paramètres!B8</f>
         <v/>
       </c>
-      <c r="C6" s="38">
+      <c r="C6" s="42">
         <f>Paramètres!C8</f>
         <v/>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="33">
         <f>'C3 C4 C5'!D31</f>
         <v/>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="34">
         <f>Paramètres!H8/365</f>
         <v/>
       </c>
-      <c r="F6" s="39">
-        <f>IF(Paramètres!B8="Vacant",'C3 C4 C5'!D31,'C3 C4 C5'!D31*(1-Paramètres!H8/365))</f>
+      <c r="F6" s="29">
+        <f>IF(Paramètres!B8="Vacant",'C3 C4 C5'!D31,'C3 C4 C5'!D31-'C3 C4 C5'!F31)</f>
         <v/>
       </c>
     </row>
@@ -5128,8 +5362,8 @@
         <f>SUM(D5:D6)</f>
         <v/>
       </c>
-      <c r="E8" s="28" t="n"/>
-      <c r="F8" s="28" t="n"/>
+      <c r="E8" s="35" t="n"/>
+      <c r="F8" s="35" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
@@ -5137,33 +5371,33 @@
           <t>Nombre de lots vacants</t>
         </is>
       </c>
-      <c r="D9" s="40">
+      <c r="D9" s="43">
         <f>COUNTIF(B5:B6,"Vacant")</f>
         <v/>
       </c>
-      <c r="E9" s="28" t="n"/>
-      <c r="F9" s="28" t="n"/>
+      <c r="E9" s="35" t="n"/>
+      <c r="F9" s="35" t="n"/>
     </row>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="19.55" customHeight="1">
-      <c r="A11" s="41" t="inlineStr">
+      <c r="A11" s="44" t="inlineStr">
         <is>
           <t>Charges non récupérables (Frais Bancaires + CAPEX)</t>
         </is>
       </c>
-      <c r="F11" s="42">
+      <c r="F11" s="45">
         <f>'Récapitulatif 2025'!E118</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="6" customHeight="1"/>
     <row r="13" ht="25.55" customHeight="1">
-      <c r="A13" s="43" t="inlineStr">
+      <c r="A13" s="46" t="inlineStr">
         <is>
           <t>TOTAL COÛT DE LA VACANCE LOCATIVE (€ HT)</t>
         </is>
       </c>
-      <c r="F13" s="44">
+      <c r="F13" s="47">
         <f>F5+F6+F11</f>
         <v/>
       </c>
@@ -5175,14 +5409,14 @@
           <t>Part vacance sur total charges site</t>
         </is>
       </c>
-      <c r="F15" s="45">
+      <c r="F15" s="48">
         <f>IF(D8&gt;0,F13/D8,0)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="6" customHeight="1"/>
     <row r="17" ht="27.75" customHeight="1">
-      <c r="A17" s="36" t="inlineStr">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>ℹ  QP annuelle = Total site HT × clé de répartition. Coût vacance = QP annuelle × fraction de l'année non occupée.</t>
         </is>

--- a/regularisation_ORMES_A_2025.xlsx
+++ b/regularisation_ORMES_A_2025.xlsx
@@ -170,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -273,6 +273,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3697,7 +3703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4326,143 +4332,188 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="7.55" customHeight="1"/>
-    <row r="31" ht="21.75" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>HONORAIRES</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15.05" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>Honoraires Gestion Technique</t>
+        </is>
+      </c>
+      <c r="D32" s="36" t="n"/>
+      <c r="E32" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="33">
+        <f>IF(D32="","",D32*E32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Sous-total — HONORAIRES</t>
+        </is>
+      </c>
+      <c r="C33" s="11">
+        <f>SUM(C32:C32)</f>
+        <v/>
+      </c>
+      <c r="D33" s="11">
+        <f>SUM(D32:D32)</f>
+        <v/>
+      </c>
+      <c r="E33" s="35" t="n"/>
+      <c r="F33" s="11">
+        <f>SUM(F32:F32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="7.55" customHeight="1"/>
+    <row r="35" ht="21.75" customHeight="1">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>TOTAL CHARGES RÉCUPÉRABLES RÉELLES (€ HT)</t>
         </is>
       </c>
-      <c r="C31" s="16">
-        <f>C9+C12+C26+C29</f>
-        <v/>
-      </c>
-      <c r="D31" s="16">
-        <f>D9+D12+D26+D29</f>
-        <v/>
-      </c>
-      <c r="E31" s="36" t="n"/>
-      <c r="F31" s="16">
-        <f>F9+F12+F26+F29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="7.55" customHeight="1"/>
-    <row r="33" ht="19.55" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="C35" s="16">
+        <f>C9+C12+C26+C29+C33</f>
+        <v/>
+      </c>
+      <c r="D35" s="16">
+        <f>D9+D12+D26+D29+D33</f>
+        <v/>
+      </c>
+      <c r="E35" s="38" t="n"/>
+      <c r="F35" s="16">
+        <f>F9+F12+F26+F29+F33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="7.55" customHeight="1"/>
+    <row r="37" ht="19.55" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>Provisions pour charges versées</t>
         </is>
       </c>
-      <c r="C33" s="37" t="n"/>
-      <c r="D33" s="27" t="inlineStr">
+      <c r="C37" s="39" t="n"/>
+      <c r="D37" s="27" t="inlineStr">
         <is>
           <t>Montant annuel (€)</t>
         </is>
       </c>
-      <c r="E33" s="37" t="n"/>
-      <c r="F33" s="27" t="inlineStr">
+      <c r="E37" s="39" t="n"/>
+      <c r="F37" s="27" t="inlineStr">
         <is>
           <t>Montant locataire (€)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15.8" customHeight="1">
-      <c r="A34" s="21" t="inlineStr">
+    <row r="38" ht="15.8" customHeight="1">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  1er trimestre (T1)</t>
         </is>
       </c>
-      <c r="F34" s="33" t="n">
+      <c r="F38" s="33" t="n">
         <v>2990.6</v>
       </c>
     </row>
-    <row r="35" ht="15.8" customHeight="1">
-      <c r="A35" s="21" t="inlineStr">
+    <row r="39" ht="15.8" customHeight="1">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  2e trimestre (T2)</t>
         </is>
       </c>
-      <c r="F35" s="33" t="n">
+      <c r="F39" s="33" t="n">
         <v>25284.11</v>
       </c>
     </row>
-    <row r="36" ht="15.8" customHeight="1">
-      <c r="A36" s="21" t="inlineStr">
+    <row r="40" ht="15.8" customHeight="1">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  3e trimestre (T3)</t>
         </is>
       </c>
-      <c r="F36" s="33" t="n">
+      <c r="F40" s="33" t="n">
         <v>28376.42</v>
       </c>
     </row>
-    <row r="37" ht="15.8" customHeight="1">
-      <c r="A37" s="21" t="inlineStr">
+    <row r="41" ht="15.8" customHeight="1">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  4e trimestre (T4)</t>
         </is>
       </c>
-      <c r="F37" s="33" t="n">
+      <c r="F41" s="33" t="n">
         <v>28376.42</v>
       </c>
     </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>Total provisions pour charges versées →</t>
         </is>
       </c>
-      <c r="D38" s="11">
-        <f>SUM(D34:D37)</f>
-        <v/>
-      </c>
-      <c r="E38" s="35" t="n"/>
-      <c r="F38" s="11">
-        <f>SUM(F34:F37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="7.55" customHeight="1"/>
-    <row r="40" ht="21.75" customHeight="1">
-      <c r="A40" s="38">
-        <f>IF(F31-F38&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
-        <v/>
-      </c>
-      <c r="D40" s="39">
-        <f>D31-D38</f>
-        <v/>
-      </c>
-      <c r="E40" s="37" t="n"/>
-      <c r="F40" s="39">
-        <f>F31-F38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="27.75" customHeight="1">
-      <c r="A42" s="40" t="inlineStr">
+      <c r="D42" s="11">
+        <f>SUM(D38:D41)</f>
+        <v/>
+      </c>
+      <c r="E42" s="35" t="n"/>
+      <c r="F42" s="11">
+        <f>SUM(F38:F41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="7.55" customHeight="1"/>
+    <row r="44" ht="21.75" customHeight="1">
+      <c r="A44" s="40">
+        <f>IF(F35-F42&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
+        <v/>
+      </c>
+      <c r="D44" s="41">
+        <f>D35-D42</f>
+        <v/>
+      </c>
+      <c r="E44" s="39" t="n"/>
+      <c r="F44" s="41">
+        <f>F35-F42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="27.75" customHeight="1">
+      <c r="A46" s="42" t="inlineStr">
         <is>
           <t>ℹ  Clé répartition = surface lot ÷ surface totale site. Période = nombre de jours d'occupation ÷ 365.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="18">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A42:C42"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A42:F42"/>
     <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A44:C44"/>
     <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A46:F46"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A37:B37"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A35:B35"/>
     <mergeCell ref="A12:B12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4475,7 +4526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5104,131 +5155,176 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="7.55" customHeight="1"/>
-    <row r="31" ht="21.75" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>HONORAIRES</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15.05" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>Honoraires Gestion Technique</t>
+        </is>
+      </c>
+      <c r="D32" s="36" t="n"/>
+      <c r="E32" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="33">
+        <f>IF(D32="","",D32*E32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Sous-total — HONORAIRES</t>
+        </is>
+      </c>
+      <c r="C33" s="11">
+        <f>SUM(C32:C32)</f>
+        <v/>
+      </c>
+      <c r="D33" s="11">
+        <f>SUM(D32:D32)</f>
+        <v/>
+      </c>
+      <c r="E33" s="35" t="n"/>
+      <c r="F33" s="11">
+        <f>SUM(F32:F32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="7.55" customHeight="1"/>
+    <row r="35" ht="21.75" customHeight="1">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>TOTAL CHARGES RÉCUPÉRABLES RÉELLES (€ HT)</t>
         </is>
       </c>
-      <c r="C31" s="16">
-        <f>C9+C12+C26+C29</f>
-        <v/>
-      </c>
-      <c r="D31" s="16">
-        <f>D9+D12+D26+D29</f>
-        <v/>
-      </c>
-      <c r="E31" s="36" t="n"/>
-      <c r="F31" s="16">
-        <f>F9+F12+F26+F29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="7.55" customHeight="1"/>
-    <row r="33" ht="19.55" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="C35" s="16">
+        <f>C9+C12+C26+C29+C33</f>
+        <v/>
+      </c>
+      <c r="D35" s="16">
+        <f>D9+D12+D26+D29+D33</f>
+        <v/>
+      </c>
+      <c r="E35" s="38" t="n"/>
+      <c r="F35" s="16">
+        <f>F9+F12+F26+F29+F33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="7.55" customHeight="1"/>
+    <row r="37" ht="19.55" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>Provisions pour charges versées</t>
         </is>
       </c>
-      <c r="C33" s="37" t="n"/>
-      <c r="D33" s="27" t="inlineStr">
+      <c r="C37" s="39" t="n"/>
+      <c r="D37" s="27" t="inlineStr">
         <is>
           <t>Montant annuel (€)</t>
         </is>
       </c>
-      <c r="E33" s="37" t="n"/>
-      <c r="F33" s="27" t="inlineStr">
+      <c r="E37" s="39" t="n"/>
+      <c r="F37" s="27" t="inlineStr">
         <is>
           <t>Montant locataire (€)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15.8" customHeight="1">
-      <c r="A34" s="21" t="inlineStr">
+    <row r="38" ht="15.8" customHeight="1">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  1er trimestre (T1)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="15.8" customHeight="1">
-      <c r="A35" s="21" t="inlineStr">
+    <row r="39" ht="15.8" customHeight="1">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  2e trimestre (T2)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15.8" customHeight="1">
-      <c r="A36" s="21" t="inlineStr">
+    <row r="40" ht="15.8" customHeight="1">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  3e trimestre (T3)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15.8" customHeight="1">
-      <c r="A37" s="21" t="inlineStr">
+    <row r="41" ht="15.8" customHeight="1">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  4e trimestre (T4)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>Total provisions pour charges versées →</t>
         </is>
       </c>
-      <c r="D38" s="11">
-        <f>SUM(D34:D37)</f>
-        <v/>
-      </c>
-      <c r="E38" s="35" t="n"/>
-      <c r="F38" s="11">
-        <f>SUM(F34:F37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="7.55" customHeight="1"/>
-    <row r="40" ht="21.75" customHeight="1">
-      <c r="A40" s="38">
-        <f>IF(F31-F38&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
-        <v/>
-      </c>
-      <c r="D40" s="39">
-        <f>D31-D38</f>
-        <v/>
-      </c>
-      <c r="E40" s="37" t="n"/>
-      <c r="F40" s="39">
-        <f>F31-F38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="27.75" customHeight="1">
-      <c r="A42" s="40" t="inlineStr">
+      <c r="D42" s="11">
+        <f>SUM(D38:D41)</f>
+        <v/>
+      </c>
+      <c r="E42" s="35" t="n"/>
+      <c r="F42" s="11">
+        <f>SUM(F38:F41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="7.55" customHeight="1"/>
+    <row r="44" ht="21.75" customHeight="1">
+      <c r="A44" s="40">
+        <f>IF(F35-F42&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
+        <v/>
+      </c>
+      <c r="D44" s="41">
+        <f>D35-D42</f>
+        <v/>
+      </c>
+      <c r="E44" s="39" t="n"/>
+      <c r="F44" s="41">
+        <f>F35-F42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="27.75" customHeight="1">
+      <c r="A46" s="42" t="inlineStr">
         <is>
           <t>ℹ  Clé répartition = surface lot ÷ surface totale site. Période = nombre de jours d'occupation ÷ 365.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="18">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A42:C42"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A42:F42"/>
     <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A44:C44"/>
     <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A46:F46"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A37:B37"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A35:B35"/>
     <mergeCell ref="A12:B12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5300,7 +5396,7 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="41">
+      <c r="A5" s="43">
         <f>Paramètres!A7</f>
         <v/>
       </c>
@@ -5308,12 +5404,12 @@
         <f>Paramètres!B7</f>
         <v/>
       </c>
-      <c r="C5" s="42">
+      <c r="C5" s="44">
         <f>Paramètres!C7</f>
         <v/>
       </c>
       <c r="D5" s="33">
-        <f>'C1 C2'!D31</f>
+        <f>'C1 C2'!D35</f>
         <v/>
       </c>
       <c r="E5" s="34">
@@ -5321,12 +5417,12 @@
         <v/>
       </c>
       <c r="F5" s="29">
-        <f>IF(Paramètres!B7="Vacant",'C1 C2'!D31,'C1 C2'!D31-'C1 C2'!F31)</f>
+        <f>IF(Paramètres!B7="Vacant",'C1 C2'!D35,'C1 C2'!D35-'C1 C2'!F35)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="41">
+      <c r="A6" s="43">
         <f>Paramètres!A8</f>
         <v/>
       </c>
@@ -5334,12 +5430,12 @@
         <f>Paramètres!B8</f>
         <v/>
       </c>
-      <c r="C6" s="42">
+      <c r="C6" s="44">
         <f>Paramètres!C8</f>
         <v/>
       </c>
       <c r="D6" s="33">
-        <f>'C3 C4 C5'!D31</f>
+        <f>'C3 C4 C5'!D35</f>
         <v/>
       </c>
       <c r="E6" s="34">
@@ -5347,7 +5443,7 @@
         <v/>
       </c>
       <c r="F6" s="29">
-        <f>IF(Paramètres!B8="Vacant",'C3 C4 C5'!D31,'C3 C4 C5'!D31-'C3 C4 C5'!F31)</f>
+        <f>IF(Paramètres!B8="Vacant",'C3 C4 C5'!D35,'C3 C4 C5'!D35-'C3 C4 C5'!F35)</f>
         <v/>
       </c>
     </row>
@@ -5371,7 +5467,7 @@
           <t>Nombre de lots vacants</t>
         </is>
       </c>
-      <c r="D9" s="43">
+      <c r="D9" s="45">
         <f>COUNTIF(B5:B6,"Vacant")</f>
         <v/>
       </c>
@@ -5380,24 +5476,24 @@
     </row>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="19.55" customHeight="1">
-      <c r="A11" s="44" t="inlineStr">
+      <c r="A11" s="46" t="inlineStr">
         <is>
           <t>Charges non récupérables (Frais Bancaires + CAPEX)</t>
         </is>
       </c>
-      <c r="F11" s="45">
+      <c r="F11" s="47">
         <f>'Récapitulatif 2025'!E118</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="6" customHeight="1"/>
     <row r="13" ht="25.55" customHeight="1">
-      <c r="A13" s="46" t="inlineStr">
+      <c r="A13" s="48" t="inlineStr">
         <is>
           <t>TOTAL COÛT DE LA VACANCE LOCATIVE (€ HT)</t>
         </is>
       </c>
-      <c r="F13" s="47">
+      <c r="F13" s="49">
         <f>F5+F6+F11</f>
         <v/>
       </c>
@@ -5409,14 +5505,14 @@
           <t>Part vacance sur total charges site</t>
         </is>
       </c>
-      <c r="F15" s="48">
+      <c r="F15" s="50">
         <f>IF(D8&gt;0,F13/D8,0)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="6" customHeight="1"/>
     <row r="17" ht="27.75" customHeight="1">
-      <c r="A17" s="40" t="inlineStr">
+      <c r="A17" s="42" t="inlineStr">
         <is>
           <t>ℹ  QP annuelle = Total site HT × clé de répartition. Coût vacance = QP annuelle × fraction de l'année non occupée.</t>
         </is>
